--- a/backend/test/data/eva_datasheet.xlsx
+++ b/backend/test/data/eva_datasheet.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hcmut\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hcmut\internship\doanhoi-portal\backend\test\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5659AFBB-93EC-42BF-9FC5-A417B37FC2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D950EE-8E69-4CBD-8C53-29D7B1440941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="667">
   <si>
     <t>BD25CTX0001</t>
   </si>
@@ -1224,12 +1235,889 @@
   <si>
     <t>Mã ctxh</t>
   </si>
+  <si>
+    <t>Lab Hàng không - Lab Tàu thủy</t>
+  </si>
+  <si>
+    <t>[GT] CTV HỖ TRỢ DỌN DẸP PHÒNG BỘ MÔN HÀNG KHÔNG</t>
+  </si>
+  <si>
+    <t>24-01-2025 -&gt; 24-01-2025</t>
+  </si>
+  <si>
+    <t>Tòa C5</t>
+  </si>
+  <si>
+    <t>[GT] CTV HỖ TRỢ ĐÓN ĐOÀN HỌC SINH</t>
+  </si>
+  <si>
+    <t>07-02-2025 -&gt; 07-02-2025</t>
+  </si>
+  <si>
+    <t>Hội trường C5, trường Đại học Bách khoa, ĐHQG-HCM, cơ sở Lý Thường Kiệt</t>
+  </si>
+  <si>
+    <t>Hỗ trợ Lễ tiếp nhận động cơ từ Công ty TNHH Việt Nam Suzuki</t>
+  </si>
+  <si>
+    <t>09-04-2025 -&gt; 09-04-2025</t>
+  </si>
+  <si>
+    <t>Hội trường 17, lầu 1, Văn phòng 2 – Bộ Giáo dục và Đào tạo</t>
+  </si>
+  <si>
+    <t>CTV LỄ VINH DANH TÀI NĂNG LƯƠNG VĂN CAN LẦN THỨ 11 VÀ PHÁT ĐỘNG GIẢI THƯỞNG LẦN THỨ 12</t>
+  </si>
+  <si>
+    <t>18-11-2025 -&gt; 18-11-2025</t>
+  </si>
+  <si>
+    <t>Đại Học Bách Khoa TPHCM - Thành Phố Dĩ An, Tỉnh Bình Dương</t>
+  </si>
+  <si>
+    <t>[FEEE] - TRỌNG TÀI HỖ TRỢ HỘI THAO KHOA ĐIỆN - ĐIỆN TỬ 2025</t>
+  </si>
+  <si>
+    <t>29-11-2025 -&gt; 06-12-2025</t>
+  </si>
+  <si>
+    <t>[FEEE] - HỖ TRỢ CÔNG TÁC HỒ SƠ PHÒNG TRÀO SINH VIÊN 5 TỐT CÁC CẤP NĂM HỌC 2024-2025</t>
+  </si>
+  <si>
+    <t>05-12-2025 -&gt; 12-12-2025</t>
+  </si>
+  <si>
+    <t>Đại Học Bách Khoa TPHCM - 268, Đường Lý Thường Kiệt, Phường 14, Quận 10, Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>[FEEE] - HOẠT ĐỘNG CTV tham gia Lễ ra quân hoạt động Môi trường xanh</t>
+  </si>
+  <si>
+    <t>14-12-2025 -&gt; 21-12-2025</t>
+  </si>
+  <si>
+    <t>[FEEE] - HOẠT ĐỘNG HỖ TRỢ DEE GAMES 2025</t>
+  </si>
+  <si>
+    <t>[FEEE] - HOẠT ĐỘNG HỖ TRỢ DEEGAMES 2025</t>
+  </si>
+  <si>
+    <t>[FEEE] - TUYỂN SINH VIÊN THAM DỰ CHƯƠNG TRÌNH GẶP GỠ CÁN BỘ ĐOÀN VÀ ĐẢNG VIÊN TRẺ KHÓA K25</t>
+  </si>
+  <si>
+    <t>[FEEE] - CTV HỖ TRỢ LỄ TỐT NGHIỆP THÁNG 11 2025</t>
+  </si>
+  <si>
+    <t>26-12-2025 -&gt; 02-01-2026</t>
+  </si>
+  <si>
+    <t>TRUONG DAI HOC BACH KHOA_CS1</t>
+  </si>
+  <si>
+    <t>TNV HO TRO PHAT HO SO CHO PHONG CTSV THANG 9 - 10.2025</t>
+  </si>
+  <si>
+    <t>17-09-2025 -&gt; 17-10-2025</t>
+  </si>
+  <si>
+    <t>Bách Khoa CS1</t>
+  </si>
+  <si>
+    <t>Hỗ t ro phát giấy chứng nhận sinh viên</t>
+  </si>
+  <si>
+    <t>07-10-2025 -&gt; 11-10-2025</t>
+  </si>
+  <si>
+    <t>Cơ sở Lý Thường Kiệt</t>
+  </si>
+  <si>
+    <t>[HH] Dọn PTN Hoá Phân tích 207 B2 tháng 4/2025</t>
+  </si>
+  <si>
+    <t>17-06-2025 -&gt; 01-07-2025</t>
+  </si>
+  <si>
+    <t>[HH] Dọn PTN Hoá Vô cơ 213 B2 tháng 12/2024</t>
+  </si>
+  <si>
+    <t>28-01-2025 -&gt; 11-02-2025</t>
+  </si>
+  <si>
+    <t>CS LTK</t>
+  </si>
+  <si>
+    <t>BTC HỘI THẢO SỨC KHỎE TOÀN DIỆN HEALTH AND WELLNESS WORKSHOP</t>
+  </si>
+  <si>
+    <t>16-07-2025 -&gt; 01-12-2025</t>
+  </si>
+  <si>
+    <t>BTC OSA PODCAST: WHISPERS OF ETERNITY</t>
+  </si>
+  <si>
+    <t>BTC WORKSHOP YONKOMA</t>
+  </si>
+  <si>
+    <t>BTC INTERNATIONAL CONNECTION FESTIVAL</t>
+  </si>
+  <si>
+    <t>BTC HOẠT ĐỘNG ƯỚC MƠ TUỔI THƠ MÙA 2 - 2025</t>
+  </si>
+  <si>
+    <t>CTV HỖ TRỢ HẬU CẦN HOẠT ĐỘNG THĂM QUÂN MÙA HÈ XANH 2025</t>
+  </si>
+  <si>
+    <t>CTV HOẠT ĐỘNG TRAO ĐỔI VĂN HÓA THÁNG 6/2025</t>
+  </si>
+  <si>
+    <t>CS 1: LTK</t>
+  </si>
+  <si>
+    <t>CTV HỖ TRỢ CÁC HOẠT ĐỘNG TRAO ĐỔI VĂN HÓA - 12/2025</t>
+  </si>
+  <si>
+    <t>10-01-2026 -&gt; 31-01-2026</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ TỔ CHỨC HỘI TRẠI TRUYỀN THỐNG OISP CAMP 2025</t>
+  </si>
+  <si>
+    <t>11-01-2026 -&gt; 31-01-2026</t>
+  </si>
+  <si>
+    <t>CTV HỖ TRỢ CÁC CÔNG TÁC HẬU CẦN CỦA VPĐTQT - 12/2025</t>
+  </si>
+  <si>
+    <t>TỔ CHỨC VÀ THAM GIA CHƯƠNG TRÌNH CHÀO ĐÓN TÂN SINH VIÊN M.O.V.E 2025</t>
+  </si>
+  <si>
+    <t>17-01-2026 -&gt; 28-02-2026</t>
+  </si>
+  <si>
+    <t>CS 1</t>
+  </si>
+  <si>
+    <t>THAM DỰ HỘI THẢO KHOA HỌC SINH VIÊN, LĨNH VỰC ĐIỆN TOÁN ĐÁM MÂY, ĐIỆN TOÁN LƯỢNG TỬ, DỮ LIỆU LỚN - 30/10/2025</t>
+  </si>
+  <si>
+    <t>20-01-2026 -&gt; 28-02-2026</t>
+  </si>
+  <si>
+    <t>Tham dự Hội nghị khoa học và công nghệ lần thứ 19: “Công nghệ chiến lược – kết nối trí tuệ - Kiến tạo đổi mới” - 21/11/2025</t>
+  </si>
+  <si>
+    <t>25-01-2026 -&gt; 28-02-2026</t>
+  </si>
+  <si>
+    <t>CTV HỖ TRỢ ĐĂNG KÝ MÔN HỌC HK2 NH 2025-2026 (HK252)</t>
+  </si>
+  <si>
+    <t>THAM GIA VÀ TỔ CHỨC HOẠT ĐỘNG OYU WORKSHOP 2026 - "SẮC VIỆT" (31/12/2025)</t>
+  </si>
+  <si>
+    <t>31-01-2026 -&gt; 28-02-2026</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ TỔ CHỨC BUỔI CHÀO MỪNG TÂN HỌC VIÊN CHƯƠNG TRÌNH IMP KHÓA 2025 - 10/01/2026</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ HỘI DIỄN VĂN NGHỆ 7.2025</t>
+  </si>
+  <si>
+    <t>01-07-2025 -&gt; 20-07-2025</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ HỘI DIỄN VĂN NGHỆ 7.2025 - 2</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ PHÂN PHÁT, THU GOM LỄ PHỤC TỐT NGHIỆP 4.2025</t>
+  </si>
+  <si>
+    <t>22-04-2025 -&gt; 29-04-2025</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ TRẠM Y TẾ 7.2025</t>
+  </si>
+  <si>
+    <t>01-07-2025 -&gt; 01-07-2025</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ LỄ BẾ MẠC BKCUP 4.2025</t>
+  </si>
+  <si>
+    <t>25-05-2025 -&gt; 25-05-2025</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ PHÒNG THÍ NGHIỆM 5.2025</t>
+  </si>
+  <si>
+    <t>26-05-2025 -&gt; 26-05-2025</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ VP ĐOÀN TRƯỜNG 5.2025</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ DỌN DẸP PTN KỸ THUẬT MỸ PHẨM 6.2025</t>
+  </si>
+  <si>
+    <t>03-07-2025 -&gt; 04-07-2025</t>
+  </si>
+  <si>
+    <t>TNV THAM GIA HỖ TRỢ CHƯƠNG TRÌNH GIẤC MƠ DU HỌC NĂM 2025</t>
+  </si>
+  <si>
+    <t>Trường Đại học Bách khoa - ĐHQG-HCM, Cơ sở Lý Thường Kiệt</t>
+  </si>
+  <si>
+    <t>- Hỗ trợ Đoàn khoa KTXD trong tháng 09 năm 2025.
+- Mọi thắc mắc vui lòng liên hệ: Nhật Thuận (Zalo: 0393873106)
+- Đây là chuỗi hoạt động hỗ trợ đoàn khoa KTXD trong tháng 09 các bạn theo dõi Fanpage Facebook Ban Công Tác Xã Hội - Khoa Kỹ Thuật Xây Dựng
+- Link fanpage: https://www.facebook.com/profile.php?id=100068133033425</t>
+  </si>
+  <si>
+    <t>17-10-2025 -&gt; 20-10-2025</t>
+  </si>
+  <si>
+    <t>- Hỗ trợ Đoàn khoa KTXD trong tháng 10 năm 2025.
+- Mọi thắc mắc vui lòng liên hệ: Nhật Thuận (Zalo: 0393873106)
+- Đây là chuỗi hoạt động hỗ trợ đoàn khoa KTXD trong tháng 10 các bạn theo dõi Fanpage Facebook Ban Công Tác Xã Hội - Khoa Kỹ Thuật Xây Dựng
+- Link fanpage: https://www.facebook.com/profile.php?id=100068133033425</t>
+  </si>
+  <si>
+    <t>16-11-2025 -&gt; 19-11-2025</t>
+  </si>
+  <si>
+    <t>- Hỗ trợ Đoàn khoa KTXD trong tháng 11 năm 2025.
+- Mọi thắc mắc vui lòng liên hệ: Hữu Danh (Zalo: 0328355041)
+- Đây là chuỗi hoạt động hỗ trợ đoàn khoa KTXD trong tháng 11 các bạn theo dõi Fanpage Facebook Ban Công Tác Xã Hội - Khoa Kỹ Thuật Xây Dựng
+- Link fanpage: https://www.facebook.com/profile.php?id=100068133033425</t>
+  </si>
+  <si>
+    <t>20-12-2025 -&gt; 31-12-2025</t>
+  </si>
+  <si>
+    <t>Trường ĐH Bách Khoa Tp. Hồ Chí Minh, cơ sở Lý Thường Kiệt</t>
+  </si>
+  <si>
+    <t>- Tổ chức lớp ôn tập khoa KTXD trong tháng 12 năm 2024.
+- Mọi thắc mắc vui lòng liên hệ: Hữu Danh (Zalo: 0328355041)
+- Link fanpage: https://www.facebook.com/profile.php?id=100068133033425</t>
+  </si>
+  <si>
+    <t>28-01-2025 -&gt; 31-01-2025</t>
+  </si>
+  <si>
+    <t>- Hỗ trợ Đoàn khoa KTXD trong tháng 12 năm 2025.
+- Mọi thắc mắc vui lòng liên hệ: Hữu Danh (Zalo: 0328355041)
+- Đây là chuỗi hoạt động hỗ trợ đoàn khoa KTXD trong tháng 12 các bạn theo dõi Fanpage Facebook Ban Công Tác Xã Hội - Khoa Kỹ Thuật Xây Dựng
+- Link fanpage: https://www.facebook.com/profile.php?id=100068133033425</t>
+  </si>
+  <si>
+    <t>18-01-2026 -&gt; 23-01-2026</t>
+  </si>
+  <si>
+    <t>- Cập nhật CTXH cho Tổ CTV Thường trực khoa KTXD tháng 09-10/2025
+- Mọi thắc mắc vui lòng liên hệ: Nguyễn Hữu Danh (0328355041)</t>
+  </si>
+  <si>
+    <t>17-01-2026 -&gt; 21-01-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GT25CTX0006 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GT25CTX0007 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GT25CTX0008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT25KKK0059 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD25KKK0013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD25KKK0014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD25KKK0015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD25KKK0016 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD25KKK0017 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD25KKK0018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD25KKK0019 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT25KKK0040 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT25KKK0041 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC25CTX0036 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC25CTX0002 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT25CTX0054 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT25CTX0055 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT25CTX0056 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT25CTX0057 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT25CTX0058 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT25CTX0059 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT25CTX0060 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT26CTX0001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT26CTX0002 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT26CTX0003 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT26CTX0004 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT26CTX0005 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT26CTX0006 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT26CTX0007 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT26CTX0008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QT26CTX0009 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV25KKK0117 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV25KKK0118 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV25KKK0119 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV25KKK0120 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV25KKK0121 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN25KKK0096 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN25KKK0095 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN25KKK0094 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN25KKK0153 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN25KKK0154 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD25CTX0011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD25CTX0012 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD25CTX0013 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD25CTX0014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD25HTR0001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD26CTX0001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD26HTR0001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD26HTR0002 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV25HMT0002 </t>
+  </si>
+  <si>
+    <t>Hiến máu tình nguyện</t>
+  </si>
+  <si>
+    <t>TNV THAM GIA HIẾN MÁU TÌNH NGUYỆN 01.2025</t>
+  </si>
+  <si>
+    <t>17/01/2025</t>
+  </si>
+  <si>
+    <t>01/04/2025</t>
+  </si>
+  <si>
+    <t>06/01/2026</t>
+  </si>
+  <si>
+    <t>22/11/2025</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t>17/12/2025</t>
+  </si>
+  <si>
+    <t>22/10/2025</t>
+  </si>
+  <si>
+    <t>31/10/2025</t>
+  </si>
+  <si>
+    <t>09/06/2025</t>
+  </si>
+  <si>
+    <t>20/01/2025</t>
+  </si>
+  <si>
+    <t>02/07/2025</t>
+  </si>
+  <si>
+    <t>12/12/2025</t>
+  </si>
+  <si>
+    <t>26/12/2025</t>
+  </si>
+  <si>
+    <t>29/12/2025</t>
+  </si>
+  <si>
+    <t>13/01/2026</t>
+  </si>
+  <si>
+    <t>25/07/2025</t>
+  </si>
+  <si>
+    <t>21/05/2025</t>
+  </si>
+  <si>
+    <t>20/05/2025</t>
+  </si>
+  <si>
+    <t>30/06/2025</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>06/01/2025</t>
+  </si>
+  <si>
+    <t>03/01/2026</t>
+  </si>
+  <si>
+    <t>06/02/2025</t>
+  </si>
+  <si>
+    <t>01-01-2025 -&gt; 07-01-2025</t>
+  </si>
+  <si>
+    <t>16/04/2025</t>
+  </si>
+  <si>
+    <t>06/06/2025</t>
+  </si>
+  <si>
+    <t>CK25MAI0003</t>
+  </si>
+  <si>
+    <t>Số 138 ấp Thiên Bình, xã Tam Phước, TP Biên Hòa, tỉnh Đồng Nai.</t>
+  </si>
+  <si>
+    <t>Hoạt động Công tác xã hội (tình nguyện) tại mái ấm, nhà mở, làng trẻ em, khu điều dưỡng cho người già…</t>
+  </si>
+  <si>
+    <t>✅Địa điểm: Số 138 ấp Thiên Bình, xã Tam Phước, TP Biên Hòa, tỉnh Đồng Nai.
+✅Nội dung hoạt động: Dọn dẹp vệ sinh tại phòng sơ sinh, dạy học, hỗ trợ công việc nhà bếp…
+✅Phương tiện: Bắt buộc di chuyển bằng xe buýt đã được Đội thuê - tập trung tại cổng KTX khu A lúc 6h30 và đi theo sự hướng dẫn của người giám sát, thu lệ phí di chuyển 50k/người.</t>
+  </si>
+  <si>
+    <t>09-03-2025 -&gt; 13-03-2025</t>
+  </si>
+  <si>
+    <t>CK25MAI0004</t>
+  </si>
+  <si>
+    <t>Số 138 ấp Thiên Bình, xã Tam Phước, TP Biên Hòa, tỉnh Đồng Nai</t>
+  </si>
+  <si>
+    <t>✅Địa điểm: Số 138 ấp Thiên Bình, xã Tam Phước, TP Biên Hòa, tỉnh Đồng Nai.
+✅Nội dung hoạt động: Dọn dẹp vệ sinh tại phòng sơ sinh, dạy học, hỗ trợ công việc nhà bếp…</t>
+  </si>
+  <si>
+    <t>16/03/2025</t>
+  </si>
+  <si>
+    <t>16-03-2025 -&gt; 19-03-2025</t>
+  </si>
+  <si>
+    <t>CK25MAI0005</t>
+  </si>
+  <si>
+    <t>1210 ĐT743A, Khu phố Tân Long, Phường Tân Đông Hiệp, Thành phố Dĩ An, Bình Dương</t>
+  </si>
+  <si>
+    <t>✅Địa điểm: 1210 ĐT743A, Khu phố Tân Long, Phường Tân Đông Hiệp, Thành phố Dĩ An, Bình Dương.
+✅Nội dung hoạt động: Dọn dẹp vệ sinh, khuân vác đồ đạc , cải tạo khuôn viên, phụ bếp, chăm sóc trẻ nhỏ, dạy học, vui chơi cùng các em,…</t>
+  </si>
+  <si>
+    <t>QL25DKT0001</t>
+  </si>
+  <si>
+    <t>Nhà văn hóa sinh viên ĐHQG</t>
+  </si>
+  <si>
+    <t>Cá danh hiệu tuyên dương khen thưởng sinh viên</t>
+  </si>
+  <si>
+    <t>SIM-PHONY OF VERSE</t>
+  </si>
+  <si>
+    <t>27/10/2025</t>
+  </si>
+  <si>
+    <t>30-10-2025 -&gt; 04-11-2025</t>
+  </si>
+  <si>
+    <t>QL25DKT0002</t>
+  </si>
+  <si>
+    <t>Hội trường C5 - CS1</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ HỘI THẢO AI APPLICATION IN HEALTHCARE</t>
+  </si>
+  <si>
+    <t>QL25DKT0003</t>
+  </si>
+  <si>
+    <t>CS1</t>
+  </si>
+  <si>
+    <t>Tham gia Hội thảo Khoa học sinh viên, lĩnh vực “Điện toán đám mây, điện toán lượng tử và dữ liệu lớn”</t>
+  </si>
+  <si>
+    <t>05/11/2025</t>
+  </si>
+  <si>
+    <t>08-11-2025 -&gt; 11-11-2025</t>
+  </si>
+  <si>
+    <t>SV25HMT0037</t>
+  </si>
+  <si>
+    <t>TNV THAM GIA HIẾN MÁU TÌNH NGUYỆN 10.2025</t>
+  </si>
+  <si>
+    <t>25/10/2025</t>
+  </si>
+  <si>
+    <t>21-10-2025 -&gt; 26-10-2025</t>
+  </si>
+  <si>
+    <t>SV25KKK0080</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ CHƯƠNG TRÌNH SÁCH CŨ TRI THỨC MỚI NĂM 2025</t>
+  </si>
+  <si>
+    <t>02-03-2025 -&gt; 23-03-2025</t>
+  </si>
+  <si>
+    <t>SV25KKK0237</t>
+  </si>
+  <si>
+    <t>Sân vận động Thống Nhất</t>
+  </si>
+  <si>
+    <t>TNV THAM GIA CỔ VŨ ĐỘI BÓNG ĐÁ CATP THUỘC KHUÔN KHỔ VÒNG 9 LPBANK V.LEAGUE 1</t>
+  </si>
+  <si>
+    <t>15/11/2025</t>
+  </si>
+  <si>
+    <t>01-11-2025 -&gt; 01-11-2025</t>
+  </si>
+  <si>
+    <t>SV25KKK0253</t>
+  </si>
+  <si>
+    <t>TP. Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>[HSV] TNV HỖ TRỢ THAM GIA CHƯƠNG TRÌNH "VINH DANH THỦ KHOA" 21/11</t>
+  </si>
+  <si>
+    <t>30/11/2025</t>
+  </si>
+  <si>
+    <t>21-11-2025 -&gt; 21-11-2025</t>
+  </si>
+  <si>
+    <t>MT25NHV0001</t>
+  </si>
+  <si>
+    <t>[MT] CTV HỖ TRỢ NGÀY HỘI VIỆC LÀM KHOA KH&amp;KTMT - JOB FAIR</t>
+  </si>
+  <si>
+    <t>02/04/2025</t>
+  </si>
+  <si>
+    <t>04-04-2025 -&gt; 31-05-2025</t>
+  </si>
+  <si>
+    <t>QL25HTR0015</t>
+  </si>
+  <si>
+    <t>286- Lý Thường Kiệt, Phường 14, Quận 10,TP. Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>Show quân sự 22/3</t>
+  </si>
+  <si>
+    <t>20-04-2025 -&gt; 24-04-2025</t>
+  </si>
+  <si>
+    <t>Tên CTXH</t>
+  </si>
+  <si>
+    <t>CTV HỖ TRỢ DỌN DẸP PHÒNG BỘ MÔN Kỹ thuật Hệ thống Công nghiệp</t>
+  </si>
+  <si>
+    <t>CTV HỖ TRỢ DỌN DẸP PHÒNG THÍ NGHIỆM 710H1 VÀ TỔ CHỨC LỄ NHẬN TÀI TRỢ TỪ CÔNG TY TNHH JABIL VIỆT NAM</t>
+  </si>
+  <si>
+    <t>CTV HỖ TRỢ DỌN DẸP, SẮP XẾP PHÒNG BỘ MÔN KTHTCN CS DĨ AN</t>
+  </si>
+  <si>
+    <t>Hỗ trợ dọn dẹp PTN Đo lường - Khoa Cơ khí</t>
+  </si>
+  <si>
+    <t>Tân Trang Bộ Môn Công Nghệ Nhiệt Lạnh (Tòa nhà B5) - Đợt 2</t>
+  </si>
+  <si>
+    <t>Tân Trang Bộ Môn Công Nghệ Nhiệt Lạnh (Tòa nhà B5) - Đợt 1</t>
+  </si>
+  <si>
+    <t>Vệ sinh PTN công nghệ thiết kế và gia công tiên tiến Khoa Cơ khí</t>
+  </si>
+  <si>
+    <t>Sắp xếp, vận chuyển bàn ghế của PTN bộ môn Chế Tạo Máy và PTN Thủy lực (Trung Tâm Bảo dưỡng công nghiệp)</t>
+  </si>
+  <si>
+    <t>Sắp xếp, vận chuyển máy móc trang thiết bị PTN bộ môn Chế Tạo Máy</t>
+  </si>
+  <si>
+    <t>CỘNG TÁC VIÊN DỌN DẸP PHÒNG 103C1</t>
+  </si>
+  <si>
+    <t>DỌN DẸP VỆ SINH VĂN PHÒNG SAU CHIẾN DỊCH MÙA HÈ XANH 2025</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ DI DỜI PHÒNG THÍ NGHIỆM 104C1 KHOA CƠ KHÍ</t>
+  </si>
+  <si>
+    <t>DỌN DẸP XƯỞNG C3</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ XƯỞNG C1 ngày 01/08/2025</t>
+  </si>
+  <si>
+    <t>SẮP XẾP BÀN, GHẾ KHU VỰC HÀNH LANG XƯỞNG C1, TÒA B11 NGÀY 01/08/2025</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ DI DỜI PHÒNG THÍ NGHIỆM NGÀY 01/08/2025</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ BỘ MÔN KỸ THUẬT HỆ THỐNG CÔNG NGHIỆP 22 - 24 -25/8/2025</t>
+  </si>
+  <si>
+    <t>CÁC HOẠT ĐỘNG DI DỜI THIẾT BỊ VÀ DỌN DẸP PHÒNG THÍ NGHIỆM THUỘC KHOA CƠ KHÍ NGÀY 17.09.2025</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ BỘ MÔN KỸ THUẬT DỆT MAY DI DỜI MÁY 24.09.2025</t>
+  </si>
+  <si>
+    <t>VỆ SINH PHÒNG THÍ NGHIỆM THIẾT KẾ VÀ GIA CÔNG TIÊN TIẾN 07.09.2025</t>
+  </si>
+  <si>
+    <t>Tham gia Tổng vệ sinh Xưởng thực hành Dệt May ngày 11.09.2025</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ BỘ MÔN KỸ THUẬT HỆ THỐNG CÔNG NGHIỆP THÁNG 10.2025</t>
+  </si>
+  <si>
+    <t>Cộng tác viên Di dời máy móc thí nghiệm sửa chửa Xưởng Thực hành Dệt May 17/9/2025</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ BỘ MÔN THIẾT KẾ MÁY DI DỜI BÀN GHẾ</t>
+  </si>
+  <si>
+    <t>TNV HỖ TRỢ DỌN DẸP, SẮP XẾP BỘ MÔN KTHTCN CS2 - 15/12/2025</t>
+  </si>
+  <si>
+    <t>TNV THAM GIA HỖ TRỢ DI DỜI, SẮP XẾP THIẾT BỊ Ở XƯỞNG CƠ KHÍ C1 NGÀY 08 - 09/12/2025</t>
+  </si>
+  <si>
+    <t>TỔ CHỨC HOẠT ĐỘNG TRUNG THU 2025 TẠI TRƯỜNG TIỂU HỌC DƯƠNG VĂN LỊCH - XÃ HIỆP PHƯỚC - TP.HCM NGÀY 04.10.2025</t>
+  </si>
+  <si>
+    <t>CTV hỗ trợ tổ chức Hội thảo “Dệt may 4.0: Hành trình tối ưu quy trình và nâng cao chất lượng bền vững”</t>
+  </si>
+  <si>
+    <t>Cộng tác viên hỗ trợ Vòng chung kết Cuộc thi “Vòng đời mới cho sản phẩm tái chế”</t>
+  </si>
+  <si>
+    <t>SV CƠ KHÍ THAM DỰ LỄ KHỞI ĐỘNG THÁNG THANH NIÊN 28/02/2025</t>
+  </si>
+  <si>
+    <t>TẾT SINH VIÊN KHOA CƠ KHÍ “MẦM XUÂN”.</t>
+  </si>
+  <si>
+    <t>HOẠT ĐỘNG ĐÓN TÂN SINH VIÊN NHÓM NGÀNH KTHTCN 2024</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ TỔ CHỨC BK FAMILY DAY 2025</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ HỘI NGHỊ SINH VIÊN KHOA CƠ KHÍ 2024-2025</t>
+  </si>
+  <si>
+    <t>SINH VIÊN CƠ KHÍ THAM GIA NGÀY ĐOÀN VIÊN 2025</t>
+  </si>
+  <si>
+    <t>TỔ CÔNG TÁC HỖ TRỢ TỔ CHỨC HỘI NGHỊ SINH VIÊN KHOA CƠ KHÍ NH 2024-2025</t>
+  </si>
+  <si>
+    <t>Hỗ Trợ Tổ Chức Hội Thảo Van Lạnh Công Nghiệp Parker Hannifin 04.04.2025</t>
+  </si>
+  <si>
+    <t>CTV HỖ TRỢ CHƯƠNG TRÌNH KỶ NIỆM 26 NĂM THÀNH LẬP BỘ MÔN KTHTCN</t>
+  </si>
+  <si>
+    <t>BTC CHƯƠNG TRÌNH KỶ NIỆM 26 NĂM THÀNH LẬP BỘ MÔN KTHTCN</t>
+  </si>
+  <si>
+    <t>Hỗ Trợ Đón Đoàn HS Các Trường THPT Đến Tham Quan Trường Đại Học Bách Khoa - DHQG-HCM Vào Ngày 12.04 và 13.04</t>
+  </si>
+  <si>
+    <t>TỔ CHỨC WORKSHOP “LEAN FUNDAMENTAL"</t>
+  </si>
+  <si>
+    <t>CTV LỄ TỐT NGHIỆP KHOA CƠ KHÍ 4-2025</t>
+  </si>
+  <si>
+    <t>TỔ CÔNG TÁC LỄ TỐT NGHIỆP KHOA CƠ KHÍ 2025</t>
+  </si>
+  <si>
+    <t>Hỗ Trợ Công Tác Kiểm Định AQAS Cho Ngành Kỹ Thuật Nhiệt</t>
+  </si>
+  <si>
+    <t>TỔ CHỨC PHÁT HÀNH CHUỖI VIDEO TIẾNG ANH "PLEC GO GO"</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ THƯỜNG TRỰC ĐOÀN - HỘI KHOA CƠ KHÍ NGÀY 03/9/2025</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ CÔNG TÁC VĂN PHÒNG ĐOÀN TN - LIÊN CHI HỘI SV KHOA CƠ KHÍ TỪ NGÀY 04/9 ĐẾN 12/9/2025</t>
+  </si>
+  <si>
+    <t>THAM GIA TỔ CHỨC LỄ ĐÓN TÂN SINH K2025 VÀ LỄ TRAO HỌC BỔNG KHOA CƠ KHÍ 05/9/2025</t>
+  </si>
+  <si>
+    <t>HỖ TRỢ CÔNG TÁC VĂN PHÒNG ĐOÀN TN - LIÊN CHI HỘI SV KHOA CƠ KHÍ TỪ NGÀY 15/9 ĐẾN 19/9/2025</t>
+  </si>
+  <si>
+    <t>[GT] HỖ TRỢ SỰ KIỆN CỦA KHOA</t>
+  </si>
+  <si>
+    <t>TNV Hỗ trợ công tác sinh viên</t>
+  </si>
+  <si>
+    <t>[XD] HOẠT ĐỘNG HỖ TRỢ ĐOÀN KHOA KTXD THÁNG 09/2025</t>
+  </si>
+  <si>
+    <t>[XD] HOẠT ĐỘNG HỖ TRỢ ĐOÀN KHOA KTXD THÁNG 10/2025</t>
+  </si>
+  <si>
+    <t>[XD] HOẠT ĐỘNG HỖ TRỢ ĐOÀN KHOA KTXD THÁNG 11/2025</t>
+  </si>
+  <si>
+    <t>[XD] HOẠT ĐỘNG HỖ TRỢ ĐOÀN KHOA KTXD THÁNG 11/2025 BỔ SUNG</t>
+  </si>
+  <si>
+    <t>[XD] TỔ CHỨC LỚP ÔN TẬP KHOA KTXD THÁNG 12/2024</t>
+  </si>
+  <si>
+    <t>[XD] HOẠT ĐỘNG HỖ TRỢ ĐOÀN KHOA KTXD THÁNG 12/2025</t>
+  </si>
+  <si>
+    <t>[XD] CTV THƯỜNG TRỰC ĐOÀN - HỘI KHOA KTXD THÁNG 09-10/2025</t>
+  </si>
+  <si>
+    <t>[XD] CTV THƯỜNG TRỰC ĐOÀN - HỘI KHOA KTXD THÁNG 11-12/2025</t>
+  </si>
+  <si>
+    <t>CTXH tại Cơ sở Bảo trợ xã hội Cô nhi Thiên Bình</t>
+  </si>
+  <si>
+    <t>CTXH TẠI TRUNG TÂM BẢO TRỢ XÃ HỘI CÔ NHI THIÊN BÌNH - T2/2025</t>
+  </si>
+  <si>
+    <t>CTXH TẠI TRUNG TÂM NHÂN ĐẠO QUÊ HƯƠNG - T2/2025</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1242,6 +2130,14 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1279,11 +2175,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1564,273 +2465,297 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="173.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="255.58203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.4140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="173.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="255.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.4140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>108</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>109</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>110</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>111</v>
-      </c>
-      <c r="G2" t="s">
-        <v>112</v>
       </c>
       <c r="H2" t="s">
         <v>112</v>
       </c>
       <c r="I2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
         <v>107</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>108</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>114</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>115</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>116</v>
       </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
       <c r="H3" t="s">
         <v>117</v>
       </c>
       <c r="I3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" t="s">
         <v>107</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>118</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>119</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>120</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>121</v>
       </c>
-      <c r="G4" t="s">
-        <v>117</v>
-      </c>
       <c r="H4" t="s">
         <v>117</v>
       </c>
       <c r="I4" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" t="s">
         <v>122</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>118</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>123</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>124</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>125</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>126</v>
       </c>
-      <c r="H5" t="s">
-        <v>117</v>
-      </c>
       <c r="I5" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" t="s">
         <v>107</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>118</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>127</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>128</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>129</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>130</v>
       </c>
-      <c r="H6" t="s">
-        <v>117</v>
-      </c>
       <c r="I6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" t="s">
         <v>107</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>118</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>127</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>128</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>129</v>
       </c>
-      <c r="G7" t="s">
-        <v>117</v>
-      </c>
       <c r="H7" t="s">
         <v>117</v>
       </c>
       <c r="I7" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" t="s">
         <v>131</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>108</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>132</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>133</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>134</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>135</v>
       </c>
-      <c r="H8" t="s">
-        <v>117</v>
-      </c>
       <c r="I8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" t="s">
         <v>131</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>108</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>137</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>138</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>139</v>
-      </c>
-      <c r="G9" t="s">
-        <v>140</v>
       </c>
       <c r="H9" t="s">
         <v>140</v>
@@ -1838,37 +2763,43 @@
       <c r="I9" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" t="s">
         <v>131</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>108</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>142</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>136</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>143</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>144</v>
-      </c>
-      <c r="H10" t="s">
-        <v>126</v>
       </c>
       <c r="I10" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1876,222 +2807,243 @@
         <v>145</v>
       </c>
       <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
         <v>108</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>145</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>136</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>143</v>
       </c>
-      <c r="G11" t="s">
-        <v>117</v>
-      </c>
       <c r="H11" t="s">
         <v>117</v>
       </c>
       <c r="I11" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" t="s">
         <v>146</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>108</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>147</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>148</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>149</v>
       </c>
-      <c r="G12" t="s">
-        <v>117</v>
-      </c>
       <c r="H12" t="s">
         <v>117</v>
       </c>
       <c r="I12" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>605</v>
+      </c>
+      <c r="C13" t="s">
         <v>150</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>108</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>151</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>152</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>153</v>
       </c>
-      <c r="G13" t="s">
-        <v>117</v>
-      </c>
       <c r="H13" t="s">
         <v>117</v>
       </c>
       <c r="I13" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>606</v>
+      </c>
+      <c r="C14" t="s">
         <v>155</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>108</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>156</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>154</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>157</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>135</v>
       </c>
-      <c r="H14" t="s">
-        <v>117</v>
-      </c>
       <c r="I14" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>607</v>
+      </c>
+      <c r="C15" t="s">
         <v>159</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>108</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>160</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>158</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>161</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>135</v>
       </c>
-      <c r="H15" t="s">
-        <v>117</v>
-      </c>
       <c r="I15" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" t="s">
         <v>131</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>108</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>162</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>163</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>164</v>
       </c>
-      <c r="G16" t="s">
-        <v>117</v>
-      </c>
       <c r="H16" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I16" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" t="s">
         <v>166</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>108</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>167</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>165</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>168</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>135</v>
       </c>
-      <c r="H17" t="s">
-        <v>117</v>
-      </c>
       <c r="I17" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>608</v>
+      </c>
+      <c r="C18" t="s">
         <v>170</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>108</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>171</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>169</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>172</v>
-      </c>
-      <c r="G18" t="s">
-        <v>112</v>
       </c>
       <c r="H18" t="s">
         <v>112</v>
@@ -2099,115 +3051,127 @@
       <c r="I18" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" t="s">
         <v>174</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>108</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>175</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>173</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>176</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>144</v>
-      </c>
-      <c r="H19" t="s">
-        <v>126</v>
       </c>
       <c r="I19" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" t="s">
         <v>178</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>108</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>179</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>177</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>180</v>
       </c>
-      <c r="G20" t="s">
-        <v>117</v>
-      </c>
       <c r="H20" t="s">
         <v>117</v>
       </c>
       <c r="I20" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21" t="s">
         <v>178</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>108</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>182</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>181</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>183</v>
       </c>
-      <c r="G21" t="s">
-        <v>117</v>
-      </c>
       <c r="H21" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I21" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>609</v>
+      </c>
+      <c r="C22" t="s">
         <v>178</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>108</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>185</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>184</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>186</v>
-      </c>
-      <c r="G22" t="s">
-        <v>187</v>
       </c>
       <c r="H22" t="s">
         <v>187</v>
@@ -2215,28 +3179,31 @@
       <c r="I22" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>610</v>
+      </c>
+      <c r="C23" t="s">
         <v>178</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>108</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>188</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>184</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>186</v>
-      </c>
-      <c r="G23" t="s">
-        <v>187</v>
       </c>
       <c r="H23" t="s">
         <v>187</v>
@@ -2244,637 +3211,703 @@
       <c r="I23" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" t="s">
         <v>190</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>108</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>191</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>189</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>192</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>135</v>
       </c>
-      <c r="H24" t="s">
-        <v>117</v>
-      </c>
       <c r="I24" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
       <c r="B25" t="s">
+        <v>611</v>
+      </c>
+      <c r="C25" t="s">
         <v>190</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>108</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>194</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>193</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>195</v>
       </c>
-      <c r="G25" t="s">
-        <v>117</v>
-      </c>
       <c r="H25" t="s">
         <v>117</v>
       </c>
       <c r="I25" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
       <c r="B26" t="s">
+        <v>612</v>
+      </c>
+      <c r="C26" t="s">
         <v>190</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>108</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>196</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>193</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>195</v>
       </c>
-      <c r="G26" t="s">
-        <v>117</v>
-      </c>
       <c r="H26" t="s">
         <v>117</v>
       </c>
       <c r="I26" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
       <c r="B27" t="s">
+        <v>613</v>
+      </c>
+      <c r="C27" t="s">
         <v>190</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>108</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>197</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>193</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>195</v>
       </c>
-      <c r="G27" t="s">
-        <v>117</v>
-      </c>
       <c r="H27" t="s">
         <v>117</v>
       </c>
       <c r="I27" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" t="s">
         <v>190</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>108</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>198</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>193</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>195</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>135</v>
       </c>
-      <c r="H28" t="s">
-        <v>117</v>
-      </c>
       <c r="I28" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
       <c r="B29" t="s">
+        <v>614</v>
+      </c>
+      <c r="C29" t="s">
         <v>190</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>108</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>200</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>199</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>201</v>
       </c>
-      <c r="G29" t="s">
-        <v>117</v>
-      </c>
       <c r="H29" t="s">
         <v>117</v>
       </c>
       <c r="I29" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
+        <v>615</v>
+      </c>
+      <c r="C30" t="s">
         <v>190</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>108</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>202</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>199</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>201</v>
       </c>
-      <c r="G30" t="s">
-        <v>117</v>
-      </c>
       <c r="H30" t="s">
         <v>117</v>
       </c>
       <c r="I30" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
       <c r="B31" t="s">
+        <v>616</v>
+      </c>
+      <c r="C31" t="s">
         <v>190</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>108</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>204</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>203</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>205</v>
       </c>
-      <c r="G31" t="s">
-        <v>117</v>
-      </c>
       <c r="H31" t="s">
         <v>117</v>
       </c>
       <c r="I31" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
       <c r="B32" t="s">
+        <v>617</v>
+      </c>
+      <c r="C32" t="s">
         <v>190</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>108</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>207</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>206</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>208</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>135</v>
       </c>
-      <c r="H32" t="s">
-        <v>117</v>
-      </c>
       <c r="I32" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
       <c r="B33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" t="s">
         <v>190</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>108</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>210</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>209</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>211</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>144</v>
       </c>
-      <c r="H33" t="s">
-        <v>117</v>
-      </c>
       <c r="I33" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
       <c r="B34" t="s">
+        <v>618</v>
+      </c>
+      <c r="C34" t="s">
         <v>190</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>108</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>212</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>213</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>214</v>
       </c>
-      <c r="G34" t="s">
-        <v>117</v>
-      </c>
       <c r="H34" t="s">
         <v>117</v>
       </c>
       <c r="I34" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>619</v>
+      </c>
+      <c r="C35" t="s">
         <v>190</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>108</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>215</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>213</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>214</v>
       </c>
-      <c r="G35" t="s">
-        <v>117</v>
-      </c>
       <c r="H35" t="s">
         <v>117</v>
       </c>
       <c r="I35" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>620</v>
+      </c>
+      <c r="C36" t="s">
         <v>190</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>108</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>216</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>213</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>214</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>144</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>126</v>
       </c>
-      <c r="I36" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" t="s">
         <v>190</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>108</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>217</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>218</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>219</v>
       </c>
-      <c r="G37" t="s">
-        <v>117</v>
-      </c>
       <c r="H37" t="s">
         <v>117</v>
       </c>
       <c r="I37" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
       <c r="B38" t="s">
+        <v>621</v>
+      </c>
+      <c r="C38" t="s">
         <v>190</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>108</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>220</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>221</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>222</v>
-      </c>
-      <c r="G38" t="s">
-        <v>126</v>
       </c>
       <c r="H38" t="s">
         <v>126</v>
       </c>
       <c r="I38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J38" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
       <c r="B39" t="s">
+        <v>622</v>
+      </c>
+      <c r="C39" t="s">
         <v>190</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>108</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>224</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>223</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>225</v>
-      </c>
-      <c r="G39" t="s">
-        <v>126</v>
       </c>
       <c r="H39" t="s">
         <v>126</v>
       </c>
       <c r="I39" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+      <c r="J39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
       <c r="B40" t="s">
+        <v>623</v>
+      </c>
+      <c r="C40" t="s">
         <v>190</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>108</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>227</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>226</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>228</v>
       </c>
-      <c r="G40" t="s">
-        <v>117</v>
-      </c>
       <c r="H40" t="s">
         <v>117</v>
       </c>
       <c r="I40" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J40" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
       <c r="B41" t="s">
+        <v>230</v>
+      </c>
+      <c r="C41" t="s">
         <v>190</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>108</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>230</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>229</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>231</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>135</v>
       </c>
-      <c r="H41" t="s">
-        <v>117</v>
-      </c>
       <c r="I41" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>233</v>
+      </c>
+      <c r="C42" t="s">
         <v>232</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>108</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>233</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>229</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>231</v>
       </c>
-      <c r="G42" t="s">
-        <v>117</v>
-      </c>
       <c r="H42" t="s">
         <v>117</v>
       </c>
       <c r="I42" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J42" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
       <c r="B43" t="s">
+        <v>624</v>
+      </c>
+      <c r="C43" t="s">
         <v>190</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>108</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>235</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>234</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>236</v>
       </c>
-      <c r="G43" t="s">
-        <v>117</v>
-      </c>
       <c r="H43" t="s">
         <v>117</v>
       </c>
       <c r="I43" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
       <c r="B44" t="s">
+        <v>625</v>
+      </c>
+      <c r="C44" t="s">
         <v>190</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>108</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>238</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>237</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>239</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>144</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
         <v>126</v>
       </c>
-      <c r="I44" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
       <c r="B45" t="s">
+        <v>626</v>
+      </c>
+      <c r="C45" t="s">
         <v>190</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>108</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>241</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>240</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>242</v>
-      </c>
-      <c r="G45" t="s">
-        <v>112</v>
       </c>
       <c r="H45" t="s">
         <v>112</v>
@@ -2882,57 +3915,63 @@
       <c r="I45" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
       <c r="B46" t="s">
+        <v>627</v>
+      </c>
+      <c r="C46" t="s">
         <v>190</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>108</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>243</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>244</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>245</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>135</v>
       </c>
-      <c r="H46" t="s">
-        <v>117</v>
-      </c>
       <c r="I46" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
       <c r="B47" t="s">
+        <v>626</v>
+      </c>
+      <c r="C47" t="s">
         <v>190</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>108</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>247</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>246</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>248</v>
-      </c>
-      <c r="G47" t="s">
-        <v>112</v>
       </c>
       <c r="H47" t="s">
         <v>112</v>
@@ -2940,86 +3979,95 @@
       <c r="I47" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J47" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
       <c r="B48" t="s">
+        <v>628</v>
+      </c>
+      <c r="C48" t="s">
         <v>190</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>108</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>250</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>249</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>251</v>
       </c>
-      <c r="G48" t="s">
-        <v>117</v>
-      </c>
       <c r="H48" t="s">
         <v>117</v>
       </c>
       <c r="I48" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
       <c r="B49" t="s">
+        <v>629</v>
+      </c>
+      <c r="C49" t="s">
         <v>252</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>108</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>253</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>249</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>251</v>
       </c>
-      <c r="G49" t="s">
-        <v>117</v>
-      </c>
       <c r="H49" t="s">
         <v>117</v>
       </c>
       <c r="I49" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J49" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
       <c r="B50" t="s">
+        <v>630</v>
+      </c>
+      <c r="C50" t="s">
         <v>190</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>108</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>254</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>255</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>256</v>
-      </c>
-      <c r="G50" t="s">
-        <v>126</v>
       </c>
       <c r="H50" t="s">
         <v>126</v>
@@ -3027,28 +4075,31 @@
       <c r="I50" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J50" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" t="s">
+        <v>631</v>
+      </c>
+      <c r="C51" t="s">
         <v>190</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>258</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>259</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>257</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>260</v>
-      </c>
-      <c r="G51" t="s">
-        <v>126</v>
       </c>
       <c r="H51" t="s">
         <v>126</v>
@@ -3056,202 +4107,223 @@
       <c r="I51" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J51" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
       <c r="B52" t="s">
+        <v>262</v>
+      </c>
+      <c r="C52" t="s">
         <v>190</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>261</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>262</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>209</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>211</v>
       </c>
-      <c r="G52" t="s">
-        <v>117</v>
-      </c>
       <c r="H52" t="s">
         <v>117</v>
       </c>
       <c r="I52" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J52" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
       <c r="B53" t="s">
+        <v>263</v>
+      </c>
+      <c r="C53" t="s">
         <v>190</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>261</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>263</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>209</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>211</v>
       </c>
-      <c r="G53" t="s">
-        <v>117</v>
-      </c>
       <c r="H53" t="s">
         <v>117</v>
       </c>
       <c r="I53" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
       <c r="B54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C54" t="s">
         <v>252</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>261</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>264</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>209</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>211</v>
       </c>
-      <c r="G54" t="s">
-        <v>117</v>
-      </c>
       <c r="H54" t="s">
         <v>117</v>
       </c>
       <c r="I54" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J54" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>53</v>
       </c>
       <c r="B55" t="s">
+        <v>265</v>
+      </c>
+      <c r="C55" t="s">
         <v>252</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>261</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>265</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>209</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>211</v>
       </c>
-      <c r="G55" t="s">
-        <v>117</v>
-      </c>
       <c r="H55" t="s">
         <v>117</v>
       </c>
       <c r="I55" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J55" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
       <c r="B56" t="s">
+        <v>267</v>
+      </c>
+      <c r="C56" t="s">
         <v>266</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>261</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>267</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>209</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>211</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>126</v>
       </c>
-      <c r="H56" t="s">
-        <v>117</v>
-      </c>
       <c r="I56" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J56" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>268</v>
+      </c>
+      <c r="C57" t="s">
         <v>266</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>261</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>268</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>209</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>211</v>
       </c>
-      <c r="G57" t="s">
-        <v>117</v>
-      </c>
       <c r="H57" t="s">
         <v>117</v>
       </c>
       <c r="I57" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J57" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
       <c r="B58" t="s">
+        <v>632</v>
+      </c>
+      <c r="C58" t="s">
         <v>190</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>261</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>270</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>269</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>271</v>
-      </c>
-      <c r="G58" t="s">
-        <v>126</v>
       </c>
       <c r="H58" t="s">
         <v>126</v>
@@ -3259,57 +4331,63 @@
       <c r="I58" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J58" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
       <c r="B59" t="s">
+        <v>272</v>
+      </c>
+      <c r="C59" t="s">
         <v>131</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>118</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>272</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>133</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>273</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>274</v>
       </c>
-      <c r="H59" t="s">
+      <c r="I59" t="s">
         <v>112</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
       <c r="B60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" t="s">
         <v>131</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>118</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>275</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>276</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>277</v>
-      </c>
-      <c r="G60" t="s">
-        <v>113</v>
       </c>
       <c r="H60" t="s">
         <v>113</v>
@@ -3317,28 +4395,31 @@
       <c r="I60" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
       <c r="B61" t="s">
+        <v>279</v>
+      </c>
+      <c r="C61" t="s">
         <v>278</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>118</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>279</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>276</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>277</v>
-      </c>
-      <c r="G61" t="s">
-        <v>126</v>
       </c>
       <c r="H61" t="s">
         <v>126</v>
@@ -3346,115 +4427,127 @@
       <c r="I61" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J61" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
       <c r="B62" t="s">
+        <v>633</v>
+      </c>
+      <c r="C62" t="s">
         <v>131</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>118</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>280</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>138</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>281</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>135</v>
       </c>
-      <c r="H62" t="s">
-        <v>117</v>
-      </c>
       <c r="I62" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J62" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
       <c r="B63" t="s">
+        <v>282</v>
+      </c>
+      <c r="C63" t="s">
         <v>131</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>118</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>282</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>138</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>281</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>135</v>
       </c>
-      <c r="H63" t="s">
-        <v>117</v>
-      </c>
       <c r="I63" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J63" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
       <c r="B64" t="s">
+        <v>283</v>
+      </c>
+      <c r="C64" t="s">
         <v>131</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>118</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>283</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>136</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>143</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>274</v>
-      </c>
-      <c r="H64" t="s">
-        <v>112</v>
       </c>
       <c r="I64" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J64" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
       <c r="B65" t="s">
+        <v>284</v>
+      </c>
+      <c r="C65" t="s">
         <v>131</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>118</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>284</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>141</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>285</v>
-      </c>
-      <c r="G65" t="s">
-        <v>126</v>
       </c>
       <c r="H65" t="s">
         <v>126</v>
@@ -3462,28 +4555,31 @@
       <c r="I65" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J65" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>64</v>
       </c>
       <c r="B66" t="s">
+        <v>286</v>
+      </c>
+      <c r="C66" t="s">
         <v>131</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>118</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>286</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>287</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>288</v>
-      </c>
-      <c r="G66" t="s">
-        <v>187</v>
       </c>
       <c r="H66" t="s">
         <v>187</v>
@@ -3491,231 +4587,255 @@
       <c r="I66" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J66" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>65</v>
       </c>
       <c r="B67" t="s">
+        <v>289</v>
+      </c>
+      <c r="C67" t="s">
         <v>131</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>118</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>289</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>290</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>288</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>187</v>
-      </c>
-      <c r="H67" t="s">
-        <v>126</v>
       </c>
       <c r="I67" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J67" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
       <c r="B68" t="s">
+        <v>291</v>
+      </c>
+      <c r="C68" t="s">
         <v>131</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>118</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>291</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>154</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>292</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>135</v>
       </c>
-      <c r="H68" t="s">
-        <v>117</v>
-      </c>
       <c r="I68" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J68" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>67</v>
       </c>
       <c r="B69" t="s">
+        <v>293</v>
+      </c>
+      <c r="C69" t="s">
         <v>131</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>118</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>293</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>154</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>292</v>
       </c>
-      <c r="G69" t="s">
-        <v>117</v>
-      </c>
       <c r="H69" t="s">
         <v>117</v>
       </c>
       <c r="I69" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J69" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>68</v>
       </c>
       <c r="B70" t="s">
+        <v>634</v>
+      </c>
+      <c r="C70" t="s">
         <v>294</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>118</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>295</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>296</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>297</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>135</v>
       </c>
-      <c r="H70" t="s">
-        <v>117</v>
-      </c>
       <c r="I70" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J70" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>69</v>
       </c>
       <c r="B71" t="s">
+        <v>298</v>
+      </c>
+      <c r="C71" t="s">
         <v>131</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>118</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>298</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>163</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>164</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>144</v>
-      </c>
-      <c r="H71" t="s">
-        <v>126</v>
       </c>
       <c r="I71" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J71" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>70</v>
       </c>
       <c r="B72" t="s">
+        <v>299</v>
+      </c>
+      <c r="C72" t="s">
         <v>131</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>118</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>299</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>163</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>164</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>135</v>
       </c>
-      <c r="H72" t="s">
-        <v>117</v>
-      </c>
       <c r="I72" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J72" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>71</v>
       </c>
       <c r="B73" t="s">
+        <v>635</v>
+      </c>
+      <c r="C73" t="s">
         <v>301</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>118</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>302</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>300</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>303</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>274</v>
       </c>
-      <c r="H73" t="s">
+      <c r="I73" t="s">
         <v>112</v>
       </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>72</v>
       </c>
       <c r="B74" t="s">
+        <v>636</v>
+      </c>
+      <c r="C74" t="s">
         <v>304</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>118</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>305</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>165</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>168</v>
-      </c>
-      <c r="G74" t="s">
-        <v>126</v>
       </c>
       <c r="H74" t="s">
         <v>126</v>
@@ -3723,28 +4843,31 @@
       <c r="I74" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J74" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>73</v>
       </c>
       <c r="B75" t="s">
+        <v>637</v>
+      </c>
+      <c r="C75" t="s">
         <v>178</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>118</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>306</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>213</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>307</v>
-      </c>
-      <c r="G75" t="s">
-        <v>112</v>
       </c>
       <c r="H75" t="s">
         <v>112</v>
@@ -3752,608 +4875,671 @@
       <c r="I75" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J75" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>74</v>
       </c>
       <c r="B76" t="s">
+        <v>638</v>
+      </c>
+      <c r="C76" t="s">
         <v>308</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>309</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>310</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>311</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>312</v>
       </c>
-      <c r="G76" t="s">
-        <v>117</v>
-      </c>
       <c r="H76" t="s">
         <v>117</v>
       </c>
       <c r="I76" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J76" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>75</v>
       </c>
       <c r="B77" t="s">
+        <v>639</v>
+      </c>
+      <c r="C77" t="s">
         <v>314</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>309</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>315</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>313</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>316</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>135</v>
       </c>
-      <c r="H77" t="s">
-        <v>117</v>
-      </c>
       <c r="I77" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J77" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>76</v>
       </c>
       <c r="B78" t="s">
+        <v>640</v>
+      </c>
+      <c r="C78" t="s">
         <v>308</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>309</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>318</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>317</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>319</v>
-      </c>
-      <c r="G78" t="s">
-        <v>126</v>
       </c>
       <c r="H78" t="s">
         <v>126</v>
       </c>
       <c r="I78" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+      <c r="J78" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>77</v>
       </c>
       <c r="B79" t="s">
+        <v>641</v>
+      </c>
+      <c r="C79" t="s">
         <v>320</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>309</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>321</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>169</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>172</v>
       </c>
-      <c r="G79" t="s">
-        <v>117</v>
-      </c>
       <c r="H79" t="s">
         <v>117</v>
       </c>
       <c r="I79" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J79" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>642</v>
+      </c>
+      <c r="C80" t="s">
         <v>294</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>309</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>323</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>322</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>324</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>144</v>
-      </c>
-      <c r="H80" t="s">
-        <v>126</v>
       </c>
       <c r="I80" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J80" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>79</v>
       </c>
       <c r="B81" t="s">
+        <v>643</v>
+      </c>
+      <c r="C81" t="s">
         <v>294</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>309</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>325</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>322</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>326</v>
       </c>
-      <c r="G81" t="s">
-        <v>117</v>
-      </c>
       <c r="H81" t="s">
         <v>117</v>
       </c>
       <c r="I81" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J81" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>80</v>
       </c>
       <c r="B82" t="s">
+        <v>644</v>
+      </c>
+      <c r="C82" t="s">
         <v>178</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>309</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>328</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>327</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>329</v>
       </c>
-      <c r="G82" t="s">
-        <v>117</v>
-      </c>
       <c r="H82" t="s">
         <v>117</v>
       </c>
       <c r="I82" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J82" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>81</v>
       </c>
       <c r="B83" t="s">
+        <v>330</v>
+      </c>
+      <c r="C83" t="s">
         <v>178</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>309</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>330</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>115</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>331</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>135</v>
       </c>
-      <c r="H83" t="s">
-        <v>117</v>
-      </c>
       <c r="I83" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J83" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>82</v>
       </c>
       <c r="B84" t="s">
+        <v>645</v>
+      </c>
+      <c r="C84" t="s">
         <v>304</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>309</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>333</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>332</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>334</v>
       </c>
-      <c r="G84" t="s">
-        <v>117</v>
-      </c>
       <c r="H84" t="s">
         <v>117</v>
       </c>
       <c r="I84" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J84" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>83</v>
       </c>
       <c r="B85" t="s">
+        <v>336</v>
+      </c>
+      <c r="C85" t="s">
         <v>178</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>309</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>336</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>335</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>337</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>135</v>
       </c>
-      <c r="H85" t="s">
-        <v>117</v>
-      </c>
       <c r="I85" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>84</v>
       </c>
       <c r="B86" t="s">
+        <v>646</v>
+      </c>
+      <c r="C86" t="s">
         <v>178</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>309</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>339</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>338</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>340</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>144</v>
       </c>
-      <c r="H86" t="s">
+      <c r="I86" t="s">
         <v>126</v>
       </c>
-      <c r="I86" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J86" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>85</v>
       </c>
       <c r="B87" t="s">
+        <v>342</v>
+      </c>
+      <c r="C87" t="s">
         <v>178</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>309</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>342</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>341</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>343</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>135</v>
       </c>
-      <c r="H87" t="s">
-        <v>117</v>
-      </c>
       <c r="I87" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J87" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>86</v>
       </c>
       <c r="B88" t="s">
+        <v>345</v>
+      </c>
+      <c r="C88" t="s">
         <v>178</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>309</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>345</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>344</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>346</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>274</v>
-      </c>
-      <c r="H88" t="s">
-        <v>112</v>
       </c>
       <c r="I88" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J88" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>87</v>
       </c>
       <c r="B89" t="s">
+        <v>348</v>
+      </c>
+      <c r="C89" t="s">
         <v>178</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>309</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>348</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>347</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>349</v>
       </c>
-      <c r="G89" t="s">
-        <v>117</v>
-      </c>
       <c r="H89" t="s">
         <v>117</v>
       </c>
       <c r="I89" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J89" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>88</v>
       </c>
       <c r="B90" t="s">
+        <v>351</v>
+      </c>
+      <c r="C90" t="s">
         <v>178</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>309</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>351</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>350</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>352</v>
       </c>
-      <c r="G90" t="s">
-        <v>117</v>
-      </c>
       <c r="H90" t="s">
         <v>117</v>
       </c>
       <c r="I90" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J90" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>89</v>
       </c>
       <c r="B91" t="s">
+        <v>647</v>
+      </c>
+      <c r="C91" t="s">
         <v>354</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>309</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>355</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>353</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>356</v>
-      </c>
-      <c r="G91" t="s">
-        <v>126</v>
       </c>
       <c r="H91" t="s">
         <v>126</v>
       </c>
       <c r="I91" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+      <c r="J91" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>90</v>
       </c>
       <c r="B92" t="s">
+        <v>359</v>
+      </c>
+      <c r="C92" t="s">
         <v>354</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>358</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>359</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>357</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>360</v>
       </c>
-      <c r="G92" t="s">
-        <v>117</v>
-      </c>
       <c r="H92" t="s">
         <v>117</v>
       </c>
       <c r="I92" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J92" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>91</v>
       </c>
       <c r="B93" t="s">
+        <v>362</v>
+      </c>
+      <c r="C93" t="s">
         <v>304</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>309</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>362</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>361</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>363</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>135</v>
       </c>
-      <c r="H93" t="s">
-        <v>117</v>
-      </c>
       <c r="I93" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J93" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>92</v>
       </c>
       <c r="B94" t="s">
+        <v>364</v>
+      </c>
+      <c r="C94" t="s">
         <v>178</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>309</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>364</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>361</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>363</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>144</v>
-      </c>
-      <c r="H94" t="s">
-        <v>126</v>
       </c>
       <c r="I94" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J94" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>93</v>
       </c>
       <c r="B95" t="s">
+        <v>365</v>
+      </c>
+      <c r="C95" t="s">
         <v>304</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>309</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>365</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>361</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>363</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>144</v>
-      </c>
-      <c r="H95" t="s">
-        <v>126</v>
       </c>
       <c r="I95" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J95" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>94</v>
       </c>
       <c r="B96" t="s">
+        <v>648</v>
+      </c>
+      <c r="C96" t="s">
         <v>178</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>309</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>366</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>184</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>186</v>
-      </c>
-      <c r="G96" t="s">
-        <v>187</v>
       </c>
       <c r="H96" t="s">
         <v>187</v>
@@ -4361,28 +5547,31 @@
       <c r="I96" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J96" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>95</v>
       </c>
       <c r="B97" t="s">
+        <v>649</v>
+      </c>
+      <c r="C97" t="s">
         <v>178</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>309</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>367</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>213</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>307</v>
-      </c>
-      <c r="G97" t="s">
-        <v>112</v>
       </c>
       <c r="H97" t="s">
         <v>112</v>
@@ -4390,86 +5579,95 @@
       <c r="I97" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J97" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>96</v>
       </c>
       <c r="B98" t="s">
+        <v>650</v>
+      </c>
+      <c r="C98" t="s">
         <v>190</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>309</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>368</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>369</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>370</v>
       </c>
-      <c r="G98" t="s">
-        <v>117</v>
-      </c>
       <c r="H98" t="s">
         <v>117</v>
       </c>
       <c r="I98" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J98" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>97</v>
       </c>
       <c r="B99" t="s">
+        <v>651</v>
+      </c>
+      <c r="C99" t="s">
         <v>190</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>309</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>371</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>372</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>373</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>144</v>
-      </c>
-      <c r="H99" t="s">
-        <v>374</v>
       </c>
       <c r="I99" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J99" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>98</v>
       </c>
       <c r="B100" t="s">
+        <v>652</v>
+      </c>
+      <c r="C100" t="s">
         <v>190</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>309</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>375</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>376</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>377</v>
-      </c>
-      <c r="G100" t="s">
-        <v>187</v>
       </c>
       <c r="H100" t="s">
         <v>187</v>
@@ -4477,37 +5675,2028 @@
       <c r="I100" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J100" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>379</v>
       </c>
       <c r="B101" t="s">
+        <v>653</v>
+      </c>
+      <c r="C101" t="s">
         <v>190</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>309</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>378</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>226</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>228</v>
       </c>
-      <c r="G101" t="s">
-        <v>117</v>
-      </c>
       <c r="H101" t="s">
         <v>117</v>
       </c>
       <c r="I101" t="s">
         <v>117</v>
+      </c>
+      <c r="J101" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>472</v>
+      </c>
+      <c r="B102" t="s">
+        <v>382</v>
+      </c>
+      <c r="C102" t="s">
+        <v>381</v>
+      </c>
+      <c r="D102" t="s">
+        <v>108</v>
+      </c>
+      <c r="E102" t="s">
+        <v>382</v>
+      </c>
+      <c r="F102" s="3">
+        <v>45674</v>
+      </c>
+      <c r="G102" t="s">
+        <v>383</v>
+      </c>
+      <c r="H102" t="s">
+        <v>117</v>
+      </c>
+      <c r="I102" t="s">
+        <v>117</v>
+      </c>
+      <c r="J102" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>473</v>
+      </c>
+      <c r="B103" t="s">
+        <v>385</v>
+      </c>
+      <c r="C103" t="s">
+        <v>384</v>
+      </c>
+      <c r="D103" t="s">
+        <v>108</v>
+      </c>
+      <c r="E103" t="s">
+        <v>385</v>
+      </c>
+      <c r="F103" t="s">
+        <v>524</v>
+      </c>
+      <c r="G103" t="s">
+        <v>386</v>
+      </c>
+      <c r="H103" t="s">
+        <v>126</v>
+      </c>
+      <c r="I103" t="s">
+        <v>126</v>
+      </c>
+      <c r="J103" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>474</v>
+      </c>
+      <c r="B104" t="s">
+        <v>654</v>
+      </c>
+      <c r="C104" t="s">
+        <v>387</v>
+      </c>
+      <c r="D104" t="s">
+        <v>108</v>
+      </c>
+      <c r="E104" t="s">
+        <v>388</v>
+      </c>
+      <c r="F104" t="s">
+        <v>525</v>
+      </c>
+      <c r="G104" t="s">
+        <v>389</v>
+      </c>
+      <c r="H104" t="s">
+        <v>112</v>
+      </c>
+      <c r="I104" t="s">
+        <v>112</v>
+      </c>
+      <c r="J104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>475</v>
+      </c>
+      <c r="B105" t="s">
+        <v>391</v>
+      </c>
+      <c r="C105" t="s">
+        <v>390</v>
+      </c>
+      <c r="D105" t="s">
+        <v>309</v>
+      </c>
+      <c r="E105" t="s">
+        <v>391</v>
+      </c>
+      <c r="F105" t="s">
+        <v>526</v>
+      </c>
+      <c r="G105" t="s">
+        <v>392</v>
+      </c>
+      <c r="H105" t="s">
+        <v>117</v>
+      </c>
+      <c r="I105" t="s">
+        <v>117</v>
+      </c>
+      <c r="J105" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>476</v>
+      </c>
+      <c r="B106" t="s">
+        <v>394</v>
+      </c>
+      <c r="C106" t="s">
+        <v>393</v>
+      </c>
+      <c r="D106" t="s">
+        <v>309</v>
+      </c>
+      <c r="E106" t="s">
+        <v>394</v>
+      </c>
+      <c r="F106" t="s">
+        <v>527</v>
+      </c>
+      <c r="G106" t="s">
+        <v>395</v>
+      </c>
+      <c r="H106" t="s">
+        <v>187</v>
+      </c>
+      <c r="I106" t="s">
+        <v>187</v>
+      </c>
+      <c r="J106" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>477</v>
+      </c>
+      <c r="B107" t="s">
+        <v>396</v>
+      </c>
+      <c r="C107" t="s">
+        <v>393</v>
+      </c>
+      <c r="D107" t="s">
+        <v>309</v>
+      </c>
+      <c r="E107" t="s">
+        <v>396</v>
+      </c>
+      <c r="F107" t="s">
+        <v>529</v>
+      </c>
+      <c r="G107" t="s">
+        <v>397</v>
+      </c>
+      <c r="H107" t="s">
+        <v>187</v>
+      </c>
+      <c r="I107" t="s">
+        <v>187</v>
+      </c>
+      <c r="J107" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>478</v>
+      </c>
+      <c r="B108" t="s">
+        <v>399</v>
+      </c>
+      <c r="C108" t="s">
+        <v>398</v>
+      </c>
+      <c r="D108" t="s">
+        <v>309</v>
+      </c>
+      <c r="E108" t="s">
+        <v>399</v>
+      </c>
+      <c r="F108" t="s">
+        <v>530</v>
+      </c>
+      <c r="G108" t="s">
+        <v>400</v>
+      </c>
+      <c r="H108" t="s">
+        <v>117</v>
+      </c>
+      <c r="I108" t="s">
+        <v>117</v>
+      </c>
+      <c r="J108" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>479</v>
+      </c>
+      <c r="B109" t="s">
+        <v>401</v>
+      </c>
+      <c r="C109" t="s">
+        <v>398</v>
+      </c>
+      <c r="D109" t="s">
+        <v>309</v>
+      </c>
+      <c r="E109" t="s">
+        <v>401</v>
+      </c>
+      <c r="F109" t="s">
+        <v>530</v>
+      </c>
+      <c r="G109" t="s">
+        <v>400</v>
+      </c>
+      <c r="H109" t="s">
+        <v>187</v>
+      </c>
+      <c r="I109" t="s">
+        <v>187</v>
+      </c>
+      <c r="J109" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>480</v>
+      </c>
+      <c r="B110" t="s">
+        <v>402</v>
+      </c>
+      <c r="C110" t="s">
+        <v>398</v>
+      </c>
+      <c r="D110" t="s">
+        <v>309</v>
+      </c>
+      <c r="E110" t="s">
+        <v>402</v>
+      </c>
+      <c r="F110" t="s">
+        <v>530</v>
+      </c>
+      <c r="G110" t="s">
+        <v>400</v>
+      </c>
+      <c r="H110" t="s">
+        <v>187</v>
+      </c>
+      <c r="I110" t="s">
+        <v>187</v>
+      </c>
+      <c r="J110" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>481</v>
+      </c>
+      <c r="B111" t="s">
+        <v>403</v>
+      </c>
+      <c r="C111" t="s">
+        <v>398</v>
+      </c>
+      <c r="D111" t="s">
+        <v>309</v>
+      </c>
+      <c r="E111" t="s">
+        <v>403</v>
+      </c>
+      <c r="F111" t="s">
+        <v>530</v>
+      </c>
+      <c r="G111" t="s">
+        <v>400</v>
+      </c>
+      <c r="H111" t="s">
+        <v>117</v>
+      </c>
+      <c r="I111" t="s">
+        <v>117</v>
+      </c>
+      <c r="J111" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>482</v>
+      </c>
+      <c r="B112" t="s">
+        <v>404</v>
+      </c>
+      <c r="C112" t="s">
+        <v>398</v>
+      </c>
+      <c r="D112" t="s">
+        <v>309</v>
+      </c>
+      <c r="E112" t="s">
+        <v>404</v>
+      </c>
+      <c r="F112" t="s">
+        <v>531</v>
+      </c>
+      <c r="G112" t="s">
+        <v>405</v>
+      </c>
+      <c r="H112" t="s">
+        <v>187</v>
+      </c>
+      <c r="I112" t="s">
+        <v>187</v>
+      </c>
+      <c r="J112" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>483</v>
+      </c>
+      <c r="B113" t="s">
+        <v>407</v>
+      </c>
+      <c r="C113" t="s">
+        <v>406</v>
+      </c>
+      <c r="D113" t="s">
+        <v>309</v>
+      </c>
+      <c r="E113" t="s">
+        <v>407</v>
+      </c>
+      <c r="F113" t="s">
+        <v>532</v>
+      </c>
+      <c r="G113" t="s">
+        <v>408</v>
+      </c>
+      <c r="H113" t="s">
+        <v>130</v>
+      </c>
+      <c r="I113" t="s">
+        <v>117</v>
+      </c>
+      <c r="J113" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>484</v>
+      </c>
+      <c r="B114" t="s">
+        <v>655</v>
+      </c>
+      <c r="C114" t="s">
+        <v>409</v>
+      </c>
+      <c r="D114" t="s">
+        <v>309</v>
+      </c>
+      <c r="E114" t="s">
+        <v>410</v>
+      </c>
+      <c r="F114" t="s">
+        <v>533</v>
+      </c>
+      <c r="G114" t="s">
+        <v>411</v>
+      </c>
+      <c r="H114" t="s">
+        <v>130</v>
+      </c>
+      <c r="I114" t="s">
+        <v>112</v>
+      </c>
+      <c r="J114" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>485</v>
+      </c>
+      <c r="B115" t="s">
+        <v>413</v>
+      </c>
+      <c r="C115" t="s">
+        <v>412</v>
+      </c>
+      <c r="D115" t="s">
+        <v>108</v>
+      </c>
+      <c r="E115" t="s">
+        <v>413</v>
+      </c>
+      <c r="F115" t="s">
+        <v>534</v>
+      </c>
+      <c r="G115" t="s">
+        <v>414</v>
+      </c>
+      <c r="H115" t="s">
+        <v>117</v>
+      </c>
+      <c r="I115" t="s">
+        <v>117</v>
+      </c>
+      <c r="J115" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>486</v>
+      </c>
+      <c r="B116" t="s">
+        <v>415</v>
+      </c>
+      <c r="C116" t="s">
+        <v>412</v>
+      </c>
+      <c r="D116" t="s">
+        <v>108</v>
+      </c>
+      <c r="E116" t="s">
+        <v>415</v>
+      </c>
+      <c r="F116" t="s">
+        <v>535</v>
+      </c>
+      <c r="G116" t="s">
+        <v>416</v>
+      </c>
+      <c r="H116" t="s">
+        <v>126</v>
+      </c>
+      <c r="I116" t="s">
+        <v>126</v>
+      </c>
+      <c r="J116" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>487</v>
+      </c>
+      <c r="B117" t="s">
+        <v>418</v>
+      </c>
+      <c r="C117" t="s">
+        <v>417</v>
+      </c>
+      <c r="D117" t="s">
+        <v>108</v>
+      </c>
+      <c r="E117" t="s">
+        <v>418</v>
+      </c>
+      <c r="F117" t="s">
+        <v>536</v>
+      </c>
+      <c r="G117" t="s">
+        <v>419</v>
+      </c>
+      <c r="H117" t="s">
+        <v>130</v>
+      </c>
+      <c r="I117" t="s">
+        <v>187</v>
+      </c>
+      <c r="J117" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>488</v>
+      </c>
+      <c r="B118" t="s">
+        <v>420</v>
+      </c>
+      <c r="C118" t="s">
+        <v>417</v>
+      </c>
+      <c r="D118" t="s">
+        <v>108</v>
+      </c>
+      <c r="E118" t="s">
+        <v>420</v>
+      </c>
+      <c r="F118" t="s">
+        <v>536</v>
+      </c>
+      <c r="G118" t="s">
+        <v>419</v>
+      </c>
+      <c r="H118" t="s">
+        <v>130</v>
+      </c>
+      <c r="I118" t="s">
+        <v>112</v>
+      </c>
+      <c r="J118" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>489</v>
+      </c>
+      <c r="B119" t="s">
+        <v>421</v>
+      </c>
+      <c r="C119" t="s">
+        <v>417</v>
+      </c>
+      <c r="D119" t="s">
+        <v>108</v>
+      </c>
+      <c r="E119" t="s">
+        <v>421</v>
+      </c>
+      <c r="F119" t="s">
+        <v>536</v>
+      </c>
+      <c r="G119" t="s">
+        <v>419</v>
+      </c>
+      <c r="H119" t="s">
+        <v>130</v>
+      </c>
+      <c r="I119" t="s">
+        <v>187</v>
+      </c>
+      <c r="J119" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>490</v>
+      </c>
+      <c r="B120" t="s">
+        <v>422</v>
+      </c>
+      <c r="C120" t="s">
+        <v>417</v>
+      </c>
+      <c r="D120" t="s">
+        <v>108</v>
+      </c>
+      <c r="E120" t="s">
+        <v>422</v>
+      </c>
+      <c r="F120" t="s">
+        <v>536</v>
+      </c>
+      <c r="G120" t="s">
+        <v>419</v>
+      </c>
+      <c r="H120" t="s">
+        <v>130</v>
+      </c>
+      <c r="I120" t="s">
+        <v>187</v>
+      </c>
+      <c r="J120" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>491</v>
+      </c>
+      <c r="B121" t="s">
+        <v>423</v>
+      </c>
+      <c r="C121" t="s">
+        <v>417</v>
+      </c>
+      <c r="D121" t="s">
+        <v>108</v>
+      </c>
+      <c r="E121" t="s">
+        <v>423</v>
+      </c>
+      <c r="F121" t="s">
+        <v>536</v>
+      </c>
+      <c r="G121" t="s">
+        <v>419</v>
+      </c>
+      <c r="H121" t="s">
+        <v>130</v>
+      </c>
+      <c r="I121" t="s">
+        <v>187</v>
+      </c>
+      <c r="J121" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>492</v>
+      </c>
+      <c r="B122" t="s">
+        <v>424</v>
+      </c>
+      <c r="C122" t="s">
+        <v>417</v>
+      </c>
+      <c r="D122" t="s">
+        <v>108</v>
+      </c>
+      <c r="E122" t="s">
+        <v>424</v>
+      </c>
+      <c r="F122" t="s">
+        <v>536</v>
+      </c>
+      <c r="G122" t="s">
+        <v>419</v>
+      </c>
+      <c r="H122" t="s">
+        <v>130</v>
+      </c>
+      <c r="I122" t="s">
+        <v>187</v>
+      </c>
+      <c r="J122" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>493</v>
+      </c>
+      <c r="B123" t="s">
+        <v>425</v>
+      </c>
+      <c r="C123" t="s">
+        <v>417</v>
+      </c>
+      <c r="D123" t="s">
+        <v>108</v>
+      </c>
+      <c r="E123" t="s">
+        <v>425</v>
+      </c>
+      <c r="F123" t="s">
+        <v>536</v>
+      </c>
+      <c r="G123" t="s">
+        <v>419</v>
+      </c>
+      <c r="H123" t="s">
+        <v>130</v>
+      </c>
+      <c r="I123" t="s">
+        <v>187</v>
+      </c>
+      <c r="J123" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>494</v>
+      </c>
+      <c r="B124" t="s">
+        <v>427</v>
+      </c>
+      <c r="C124" t="s">
+        <v>426</v>
+      </c>
+      <c r="D124" t="s">
+        <v>108</v>
+      </c>
+      <c r="E124" t="s">
+        <v>427</v>
+      </c>
+      <c r="F124" t="s">
+        <v>537</v>
+      </c>
+      <c r="G124" t="s">
+        <v>428</v>
+      </c>
+      <c r="H124" t="s">
+        <v>130</v>
+      </c>
+      <c r="I124" t="s">
+        <v>187</v>
+      </c>
+      <c r="J124" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>495</v>
+      </c>
+      <c r="B125" t="s">
+        <v>429</v>
+      </c>
+      <c r="C125" t="s">
+        <v>426</v>
+      </c>
+      <c r="D125" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" t="s">
+        <v>429</v>
+      </c>
+      <c r="F125" t="s">
+        <v>538</v>
+      </c>
+      <c r="G125" t="s">
+        <v>430</v>
+      </c>
+      <c r="H125" t="s">
+        <v>130</v>
+      </c>
+      <c r="I125" t="s">
+        <v>187</v>
+      </c>
+      <c r="J125" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>496</v>
+      </c>
+      <c r="B126" t="s">
+        <v>431</v>
+      </c>
+      <c r="C126" t="s">
+        <v>426</v>
+      </c>
+      <c r="D126" t="s">
+        <v>108</v>
+      </c>
+      <c r="E126" t="s">
+        <v>431</v>
+      </c>
+      <c r="F126" t="s">
+        <v>538</v>
+      </c>
+      <c r="G126" t="s">
+        <v>430</v>
+      </c>
+      <c r="H126" t="s">
+        <v>130</v>
+      </c>
+      <c r="I126" t="s">
+        <v>112</v>
+      </c>
+      <c r="J126" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>497</v>
+      </c>
+      <c r="B127" t="s">
+        <v>432</v>
+      </c>
+      <c r="C127" t="s">
+        <v>426</v>
+      </c>
+      <c r="D127" t="s">
+        <v>108</v>
+      </c>
+      <c r="E127" t="s">
+        <v>432</v>
+      </c>
+      <c r="F127" t="s">
+        <v>539</v>
+      </c>
+      <c r="G127" t="s">
+        <v>433</v>
+      </c>
+      <c r="H127" t="s">
+        <v>130</v>
+      </c>
+      <c r="I127" t="s">
+        <v>187</v>
+      </c>
+      <c r="J127" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>498</v>
+      </c>
+      <c r="B128" t="s">
+        <v>435</v>
+      </c>
+      <c r="C128" t="s">
+        <v>434</v>
+      </c>
+      <c r="D128" t="s">
+        <v>108</v>
+      </c>
+      <c r="E128" t="s">
+        <v>435</v>
+      </c>
+      <c r="F128" t="s">
+        <v>526</v>
+      </c>
+      <c r="G128" t="s">
+        <v>436</v>
+      </c>
+      <c r="H128" t="s">
+        <v>130</v>
+      </c>
+      <c r="I128" t="s">
+        <v>117</v>
+      </c>
+      <c r="J128" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>499</v>
+      </c>
+      <c r="B129" t="s">
+        <v>437</v>
+      </c>
+      <c r="C129" t="s">
+        <v>434</v>
+      </c>
+      <c r="D129" t="s">
+        <v>108</v>
+      </c>
+      <c r="E129" t="s">
+        <v>437</v>
+      </c>
+      <c r="F129" t="s">
+        <v>526</v>
+      </c>
+      <c r="G129" t="s">
+        <v>438</v>
+      </c>
+      <c r="H129" t="s">
+        <v>130</v>
+      </c>
+      <c r="I129" t="s">
+        <v>117</v>
+      </c>
+      <c r="J129" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>500</v>
+      </c>
+      <c r="B130" t="s">
+        <v>439</v>
+      </c>
+      <c r="C130" t="s">
+        <v>434</v>
+      </c>
+      <c r="D130" t="s">
+        <v>108</v>
+      </c>
+      <c r="E130" t="s">
+        <v>439</v>
+      </c>
+      <c r="F130" t="s">
+        <v>526</v>
+      </c>
+      <c r="G130" t="s">
+        <v>438</v>
+      </c>
+      <c r="H130" t="s">
+        <v>130</v>
+      </c>
+      <c r="I130" t="s">
+        <v>187</v>
+      </c>
+      <c r="J130" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>501</v>
+      </c>
+      <c r="B131" t="s">
+        <v>440</v>
+      </c>
+      <c r="C131" t="s">
+        <v>434</v>
+      </c>
+      <c r="D131" t="s">
+        <v>108</v>
+      </c>
+      <c r="E131" t="s">
+        <v>440</v>
+      </c>
+      <c r="F131" t="s">
+        <v>540</v>
+      </c>
+      <c r="G131" t="s">
+        <v>441</v>
+      </c>
+      <c r="H131" t="s">
+        <v>130</v>
+      </c>
+      <c r="I131" t="s">
+        <v>187</v>
+      </c>
+      <c r="J131" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>502</v>
+      </c>
+      <c r="B132" t="s">
+        <v>442</v>
+      </c>
+      <c r="C132" t="s">
+        <v>434</v>
+      </c>
+      <c r="D132" t="s">
+        <v>108</v>
+      </c>
+      <c r="E132" t="s">
+        <v>442</v>
+      </c>
+      <c r="F132" t="s">
+        <v>540</v>
+      </c>
+      <c r="G132" t="s">
+        <v>441</v>
+      </c>
+      <c r="H132" t="s">
+        <v>130</v>
+      </c>
+      <c r="I132" t="s">
+        <v>126</v>
+      </c>
+      <c r="J132" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>503</v>
+      </c>
+      <c r="B133" t="s">
+        <v>443</v>
+      </c>
+      <c r="C133" t="s">
+        <v>107</v>
+      </c>
+      <c r="D133" t="s">
+        <v>309</v>
+      </c>
+      <c r="E133" t="s">
+        <v>443</v>
+      </c>
+      <c r="F133" t="s">
+        <v>541</v>
+      </c>
+      <c r="G133" t="s">
+        <v>444</v>
+      </c>
+      <c r="H133" t="s">
+        <v>130</v>
+      </c>
+      <c r="I133" t="s">
+        <v>117</v>
+      </c>
+      <c r="J133" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>504</v>
+      </c>
+      <c r="B134" t="s">
+        <v>445</v>
+      </c>
+      <c r="C134" t="s">
+        <v>107</v>
+      </c>
+      <c r="D134" t="s">
+        <v>309</v>
+      </c>
+      <c r="E134" t="s">
+        <v>445</v>
+      </c>
+      <c r="F134" t="s">
+        <v>541</v>
+      </c>
+      <c r="G134" t="s">
+        <v>444</v>
+      </c>
+      <c r="H134" t="s">
+        <v>130</v>
+      </c>
+      <c r="I134" t="s">
+        <v>117</v>
+      </c>
+      <c r="J134" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>505</v>
+      </c>
+      <c r="B135" t="s">
+        <v>445</v>
+      </c>
+      <c r="C135" t="s">
+        <v>107</v>
+      </c>
+      <c r="D135" t="s">
+        <v>309</v>
+      </c>
+      <c r="E135" t="s">
+        <v>445</v>
+      </c>
+      <c r="F135" t="s">
+        <v>541</v>
+      </c>
+      <c r="G135" t="s">
+        <v>444</v>
+      </c>
+      <c r="H135" t="s">
+        <v>130</v>
+      </c>
+      <c r="I135" t="s">
+        <v>117</v>
+      </c>
+      <c r="J135" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>506</v>
+      </c>
+      <c r="B136" t="s">
+        <v>446</v>
+      </c>
+      <c r="C136" t="s">
+        <v>107</v>
+      </c>
+      <c r="D136" t="s">
+        <v>309</v>
+      </c>
+      <c r="E136" t="s">
+        <v>446</v>
+      </c>
+      <c r="F136" t="s">
+        <v>541</v>
+      </c>
+      <c r="G136" t="s">
+        <v>447</v>
+      </c>
+      <c r="H136" t="s">
+        <v>130</v>
+      </c>
+      <c r="I136" t="s">
+        <v>117</v>
+      </c>
+      <c r="J136" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>507</v>
+      </c>
+      <c r="B137" t="s">
+        <v>448</v>
+      </c>
+      <c r="C137" t="s">
+        <v>107</v>
+      </c>
+      <c r="D137" t="s">
+        <v>309</v>
+      </c>
+      <c r="E137" t="s">
+        <v>448</v>
+      </c>
+      <c r="F137" t="s">
+        <v>541</v>
+      </c>
+      <c r="G137" t="s">
+        <v>449</v>
+      </c>
+      <c r="H137" t="s">
+        <v>130</v>
+      </c>
+      <c r="I137" t="s">
+        <v>117</v>
+      </c>
+      <c r="J137" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>508</v>
+      </c>
+      <c r="B138" t="s">
+        <v>450</v>
+      </c>
+      <c r="C138" t="s">
+        <v>107</v>
+      </c>
+      <c r="D138" t="s">
+        <v>309</v>
+      </c>
+      <c r="E138" t="s">
+        <v>450</v>
+      </c>
+      <c r="F138" t="s">
+        <v>542</v>
+      </c>
+      <c r="G138" t="s">
+        <v>451</v>
+      </c>
+      <c r="H138" t="s">
+        <v>117</v>
+      </c>
+      <c r="I138" t="s">
+        <v>117</v>
+      </c>
+      <c r="J138" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>509</v>
+      </c>
+      <c r="B139" t="s">
+        <v>452</v>
+      </c>
+      <c r="C139" t="s">
+        <v>107</v>
+      </c>
+      <c r="D139" t="s">
+        <v>309</v>
+      </c>
+      <c r="E139" t="s">
+        <v>452</v>
+      </c>
+      <c r="F139" t="s">
+        <v>542</v>
+      </c>
+      <c r="G139" t="s">
+        <v>453</v>
+      </c>
+      <c r="H139" t="s">
+        <v>117</v>
+      </c>
+      <c r="I139" t="s">
+        <v>117</v>
+      </c>
+      <c r="J139" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>510</v>
+      </c>
+      <c r="B140" t="s">
+        <v>454</v>
+      </c>
+      <c r="C140" t="s">
+        <v>107</v>
+      </c>
+      <c r="D140" t="s">
+        <v>309</v>
+      </c>
+      <c r="E140" t="s">
+        <v>454</v>
+      </c>
+      <c r="F140" t="s">
+        <v>543</v>
+      </c>
+      <c r="G140" t="s">
+        <v>451</v>
+      </c>
+      <c r="H140" t="s">
+        <v>117</v>
+      </c>
+      <c r="I140" t="s">
+        <v>117</v>
+      </c>
+      <c r="J140" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>511</v>
+      </c>
+      <c r="B141" t="s">
+        <v>455</v>
+      </c>
+      <c r="C141" t="s">
+        <v>107</v>
+      </c>
+      <c r="D141" t="s">
+        <v>309</v>
+      </c>
+      <c r="E141" t="s">
+        <v>455</v>
+      </c>
+      <c r="F141" t="s">
+        <v>544</v>
+      </c>
+      <c r="G141" t="s">
+        <v>456</v>
+      </c>
+      <c r="H141" t="s">
+        <v>117</v>
+      </c>
+      <c r="I141" t="s">
+        <v>117</v>
+      </c>
+      <c r="J141" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>512</v>
+      </c>
+      <c r="B142" t="s">
+        <v>457</v>
+      </c>
+      <c r="C142" t="s">
+        <v>107</v>
+      </c>
+      <c r="D142" t="s">
+        <v>309</v>
+      </c>
+      <c r="E142" t="s">
+        <v>457</v>
+      </c>
+      <c r="F142" t="s">
+        <v>544</v>
+      </c>
+      <c r="G142" t="s">
+        <v>456</v>
+      </c>
+      <c r="H142" t="s">
+        <v>117</v>
+      </c>
+      <c r="I142" t="s">
+        <v>117</v>
+      </c>
+      <c r="J142" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>513</v>
+      </c>
+      <c r="B143" t="s">
+        <v>656</v>
+      </c>
+      <c r="C143" t="s">
+        <v>458</v>
+      </c>
+      <c r="D143" t="s">
+        <v>108</v>
+      </c>
+      <c r="E143" t="s">
+        <v>459</v>
+      </c>
+      <c r="F143" t="s">
+        <v>376</v>
+      </c>
+      <c r="G143" t="s">
+        <v>460</v>
+      </c>
+      <c r="H143" t="s">
+        <v>113</v>
+      </c>
+      <c r="I143" t="s">
+        <v>113</v>
+      </c>
+      <c r="J143" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>514</v>
+      </c>
+      <c r="B144" t="s">
+        <v>657</v>
+      </c>
+      <c r="C144" t="s">
+        <v>458</v>
+      </c>
+      <c r="D144" t="s">
+        <v>108</v>
+      </c>
+      <c r="E144" t="s">
+        <v>461</v>
+      </c>
+      <c r="F144" t="s">
+        <v>240</v>
+      </c>
+      <c r="G144" t="s">
+        <v>462</v>
+      </c>
+      <c r="H144" t="s">
+        <v>374</v>
+      </c>
+      <c r="I144" t="s">
+        <v>374</v>
+      </c>
+      <c r="J144" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>515</v>
+      </c>
+      <c r="B145" t="s">
+        <v>658</v>
+      </c>
+      <c r="C145" t="s">
+        <v>458</v>
+      </c>
+      <c r="D145" t="s">
+        <v>108</v>
+      </c>
+      <c r="E145" t="s">
+        <v>463</v>
+      </c>
+      <c r="F145" t="s">
+        <v>545</v>
+      </c>
+      <c r="G145" t="s">
+        <v>464</v>
+      </c>
+      <c r="H145" t="s">
+        <v>374</v>
+      </c>
+      <c r="I145" t="s">
+        <v>374</v>
+      </c>
+      <c r="J145" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>516</v>
+      </c>
+      <c r="B146" t="s">
+        <v>659</v>
+      </c>
+      <c r="C146" t="s">
+        <v>458</v>
+      </c>
+      <c r="D146" t="s">
+        <v>108</v>
+      </c>
+      <c r="E146" t="s">
+        <v>463</v>
+      </c>
+      <c r="F146" t="s">
+        <v>545</v>
+      </c>
+      <c r="G146" t="s">
+        <v>464</v>
+      </c>
+      <c r="H146" t="s">
+        <v>374</v>
+      </c>
+      <c r="I146" t="s">
+        <v>374</v>
+      </c>
+      <c r="J146" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>517</v>
+      </c>
+      <c r="B147" t="s">
+        <v>660</v>
+      </c>
+      <c r="C147" t="s">
+        <v>465</v>
+      </c>
+      <c r="D147" t="s">
+        <v>118</v>
+      </c>
+      <c r="E147" t="s">
+        <v>466</v>
+      </c>
+      <c r="F147" t="s">
+        <v>546</v>
+      </c>
+      <c r="G147" t="s">
+        <v>467</v>
+      </c>
+      <c r="H147" t="s">
+        <v>187</v>
+      </c>
+      <c r="I147" t="s">
+        <v>187</v>
+      </c>
+      <c r="J147" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>518</v>
+      </c>
+      <c r="B148" t="s">
+        <v>661</v>
+      </c>
+      <c r="C148" t="s">
+        <v>458</v>
+      </c>
+      <c r="D148" t="s">
+        <v>108</v>
+      </c>
+      <c r="E148" t="s">
+        <v>468</v>
+      </c>
+      <c r="F148" t="s">
+        <v>547</v>
+      </c>
+      <c r="G148" t="s">
+        <v>469</v>
+      </c>
+      <c r="H148" t="s">
+        <v>374</v>
+      </c>
+      <c r="I148" t="s">
+        <v>374</v>
+      </c>
+      <c r="J148" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>519</v>
+      </c>
+      <c r="B149" t="s">
+        <v>662</v>
+      </c>
+      <c r="C149" t="s">
+        <v>458</v>
+      </c>
+      <c r="D149" t="s">
+        <v>118</v>
+      </c>
+      <c r="E149" t="s">
+        <v>470</v>
+      </c>
+      <c r="F149" t="s">
+        <v>526</v>
+      </c>
+      <c r="G149" t="s">
+        <v>471</v>
+      </c>
+      <c r="H149" t="s">
+        <v>187</v>
+      </c>
+      <c r="I149" t="s">
+        <v>187</v>
+      </c>
+      <c r="J149" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>520</v>
+      </c>
+      <c r="B150" t="s">
+        <v>663</v>
+      </c>
+      <c r="C150" t="s">
+        <v>458</v>
+      </c>
+      <c r="D150" t="s">
+        <v>118</v>
+      </c>
+      <c r="E150" t="s">
+        <v>470</v>
+      </c>
+      <c r="F150" t="s">
+        <v>526</v>
+      </c>
+      <c r="G150" t="s">
+        <v>471</v>
+      </c>
+      <c r="H150" t="s">
+        <v>187</v>
+      </c>
+      <c r="I150" t="s">
+        <v>187</v>
+      </c>
+      <c r="J150" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>521</v>
+      </c>
+      <c r="B151" t="s">
+        <v>523</v>
+      </c>
+      <c r="C151" t="s">
+        <v>107</v>
+      </c>
+      <c r="D151" t="s">
+        <v>522</v>
+      </c>
+      <c r="E151" t="s">
+        <v>523</v>
+      </c>
+      <c r="F151" t="s">
+        <v>548</v>
+      </c>
+      <c r="G151" t="s">
+        <v>549</v>
+      </c>
+      <c r="H151" t="s">
+        <v>130</v>
+      </c>
+      <c r="I151" t="s">
+        <v>117</v>
+      </c>
+      <c r="J151" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>552</v>
+      </c>
+      <c r="B152" t="s">
+        <v>664</v>
+      </c>
+      <c r="C152" t="s">
+        <v>553</v>
+      </c>
+      <c r="D152" t="s">
+        <v>554</v>
+      </c>
+      <c r="E152" t="s">
+        <v>555</v>
+      </c>
+      <c r="F152" t="s">
+        <v>120</v>
+      </c>
+      <c r="G152" t="s">
+        <v>556</v>
+      </c>
+      <c r="H152" t="s">
+        <v>274</v>
+      </c>
+      <c r="I152" t="s">
+        <v>126</v>
+      </c>
+      <c r="J152" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>557</v>
+      </c>
+      <c r="B153" t="s">
+        <v>665</v>
+      </c>
+      <c r="C153" t="s">
+        <v>558</v>
+      </c>
+      <c r="D153" t="s">
+        <v>554</v>
+      </c>
+      <c r="E153" t="s">
+        <v>559</v>
+      </c>
+      <c r="F153" t="s">
+        <v>560</v>
+      </c>
+      <c r="G153" t="s">
+        <v>561</v>
+      </c>
+      <c r="H153" t="s">
+        <v>144</v>
+      </c>
+      <c r="I153" t="s">
+        <v>126</v>
+      </c>
+      <c r="J153" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>562</v>
+      </c>
+      <c r="B154" t="s">
+        <v>666</v>
+      </c>
+      <c r="C154" t="s">
+        <v>563</v>
+      </c>
+      <c r="D154" t="s">
+        <v>554</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="F154" t="s">
+        <v>560</v>
+      </c>
+      <c r="G154" t="s">
+        <v>561</v>
+      </c>
+      <c r="H154" t="s">
+        <v>117</v>
+      </c>
+      <c r="I154" t="s">
+        <v>126</v>
+      </c>
+      <c r="J154" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>565</v>
+      </c>
+      <c r="B155" t="s">
+        <v>568</v>
+      </c>
+      <c r="C155" t="s">
+        <v>566</v>
+      </c>
+      <c r="D155" t="s">
+        <v>567</v>
+      </c>
+      <c r="E155" t="s">
+        <v>568</v>
+      </c>
+      <c r="F155" t="s">
+        <v>569</v>
+      </c>
+      <c r="G155" t="s">
+        <v>570</v>
+      </c>
+      <c r="H155" t="s">
+        <v>187</v>
+      </c>
+      <c r="I155" t="s">
+        <v>187</v>
+      </c>
+      <c r="J155" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>571</v>
+      </c>
+      <c r="B156" t="s">
+        <v>573</v>
+      </c>
+      <c r="C156" t="s">
+        <v>572</v>
+      </c>
+      <c r="D156" t="s">
+        <v>567</v>
+      </c>
+      <c r="E156" t="s">
+        <v>573</v>
+      </c>
+      <c r="F156" t="s">
+        <v>569</v>
+      </c>
+      <c r="G156" t="s">
+        <v>570</v>
+      </c>
+      <c r="H156" t="s">
+        <v>126</v>
+      </c>
+      <c r="I156" t="s">
+        <v>126</v>
+      </c>
+      <c r="J156" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>574</v>
+      </c>
+      <c r="B157" t="s">
+        <v>576</v>
+      </c>
+      <c r="C157" t="s">
+        <v>575</v>
+      </c>
+      <c r="D157" t="s">
+        <v>567</v>
+      </c>
+      <c r="E157" t="s">
+        <v>576</v>
+      </c>
+      <c r="F157" t="s">
+        <v>577</v>
+      </c>
+      <c r="G157" t="s">
+        <v>578</v>
+      </c>
+      <c r="H157" t="s">
+        <v>126</v>
+      </c>
+      <c r="I157" t="s">
+        <v>117</v>
+      </c>
+      <c r="J157" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>579</v>
+      </c>
+      <c r="B158" t="s">
+        <v>580</v>
+      </c>
+      <c r="C158" t="s">
+        <v>107</v>
+      </c>
+      <c r="D158" t="s">
+        <v>522</v>
+      </c>
+      <c r="E158" t="s">
+        <v>580</v>
+      </c>
+      <c r="F158" t="s">
+        <v>581</v>
+      </c>
+      <c r="G158" t="s">
+        <v>582</v>
+      </c>
+      <c r="H158" t="s">
+        <v>130</v>
+      </c>
+      <c r="I158" t="s">
+        <v>117</v>
+      </c>
+      <c r="J158" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>583</v>
+      </c>
+      <c r="B159" t="s">
+        <v>584</v>
+      </c>
+      <c r="C159" t="s">
+        <v>107</v>
+      </c>
+      <c r="D159" t="s">
+        <v>309</v>
+      </c>
+      <c r="E159" t="s">
+        <v>584</v>
+      </c>
+      <c r="F159" t="s">
+        <v>551</v>
+      </c>
+      <c r="G159" t="s">
+        <v>585</v>
+      </c>
+      <c r="H159" t="s">
+        <v>130</v>
+      </c>
+      <c r="I159" t="s">
+        <v>117</v>
+      </c>
+      <c r="J159" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>586</v>
+      </c>
+      <c r="B160" t="s">
+        <v>588</v>
+      </c>
+      <c r="C160" t="s">
+        <v>587</v>
+      </c>
+      <c r="D160" t="s">
+        <v>309</v>
+      </c>
+      <c r="E160" t="s">
+        <v>588</v>
+      </c>
+      <c r="F160" t="s">
+        <v>589</v>
+      </c>
+      <c r="G160" t="s">
+        <v>590</v>
+      </c>
+      <c r="H160" t="s">
+        <v>117</v>
+      </c>
+      <c r="I160" t="s">
+        <v>117</v>
+      </c>
+      <c r="J160" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>591</v>
+      </c>
+      <c r="B161" t="s">
+        <v>593</v>
+      </c>
+      <c r="C161" t="s">
+        <v>592</v>
+      </c>
+      <c r="D161" t="s">
+        <v>309</v>
+      </c>
+      <c r="E161" t="s">
+        <v>593</v>
+      </c>
+      <c r="F161" t="s">
+        <v>594</v>
+      </c>
+      <c r="G161" t="s">
+        <v>595</v>
+      </c>
+      <c r="H161" t="s">
+        <v>117</v>
+      </c>
+      <c r="I161" t="s">
+        <v>117</v>
+      </c>
+      <c r="J161" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>596</v>
+      </c>
+      <c r="B162" t="s">
+        <v>597</v>
+      </c>
+      <c r="C162" t="s">
+        <v>107</v>
+      </c>
+      <c r="D162" t="s">
+        <v>358</v>
+      </c>
+      <c r="E162" t="s">
+        <v>597</v>
+      </c>
+      <c r="F162" t="s">
+        <v>598</v>
+      </c>
+      <c r="G162" t="s">
+        <v>599</v>
+      </c>
+      <c r="H162" t="s">
+        <v>187</v>
+      </c>
+      <c r="I162" t="s">
+        <v>187</v>
+      </c>
+      <c r="J162" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>600</v>
+      </c>
+      <c r="B163" t="s">
+        <v>602</v>
+      </c>
+      <c r="C163" t="s">
+        <v>601</v>
+      </c>
+      <c r="D163" t="s">
+        <v>118</v>
+      </c>
+      <c r="E163" t="s">
+        <v>602</v>
+      </c>
+      <c r="F163" t="s">
+        <v>550</v>
+      </c>
+      <c r="G163" t="s">
+        <v>603</v>
+      </c>
+      <c r="H163" t="s">
+        <v>126</v>
+      </c>
+      <c r="I163" t="s">
+        <v>126</v>
+      </c>
+      <c r="J163" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>